--- a/Rangesayacv7.xlsx
+++ b/Rangesayacv7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\Downloads\IpekyolRangeSayac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{767C9868-3D70-4342-B21F-43CD5DFE309E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CDDB19-C1ED-49E3-99CE-A84BD5702DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{586848BF-8DA1-41BE-9680-FDF5F1E34B0D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{586848BF-8DA1-41BE-9680-FDF5F1E34B0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$M$488</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$M$652</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sayfa2!$G$1:$J$180</definedName>
     <definedName name="ara">IF(ISERROR(VLOOKUP([1]!Tablo_PRODYOLURT2012_kaynağından_sorgula4[[#This Row],[Ops]],[1]Resimsiz!XFD:A,2,0)),"yok",IF(VLOOKUP([1]!Tablo_PRODYOLURT2012_kaynağından_sorgula4[[#This Row],[Ops]],[1]Resimsiz!XFD:A,2,0)="","var",VLOOKUP([1]!Tablo_PRODYOLURT2012_kaynağından_sorgula4[[#This Row],[Ops]],[1]Resimsiz!XFD:A,2,0)))</definedName>
     <definedName name="mu">IF(ISERROR(VLOOKUP(#REF!,#REF!,2,0)),"yok",IF(VLOOKUP(#REF!,#REF!,2,0)="","var",VLOOKUP(#REF!,#REF!,2,0)))</definedName>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3843" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4827" uniqueCount="326">
   <si>
     <t>Marka</t>
   </si>
@@ -981,13 +981,58 @@
   </si>
   <si>
     <t>d</t>
+  </si>
+  <si>
+    <t>SUNI KURK</t>
+  </si>
+  <si>
+    <t>YELEK</t>
+  </si>
+  <si>
+    <t>KABAN</t>
+  </si>
+  <si>
+    <t>YAKA</t>
+  </si>
+  <si>
+    <t>DETAY</t>
+  </si>
+  <si>
+    <t>FİT</t>
+  </si>
+  <si>
+    <t>KOL BOYU</t>
+  </si>
+  <si>
+    <t>KUMAŞ TİPİ</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>Gömlek yaka</t>
+  </si>
+  <si>
+    <t>Slim fit</t>
+  </si>
+  <si>
+    <t>Tünel detayı</t>
+  </si>
+  <si>
+    <t>Kalça üstü</t>
+  </si>
+  <si>
+    <t>Diz altı</t>
+  </si>
+  <si>
+    <t>Bilek boy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1010,6 +1055,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="162"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1099,7 +1151,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1118,9 +1170,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1597,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6820A2-C4B6-4EF0-94DD-4395E6273D53}">
-  <dimension ref="A1:M488"/>
+  <dimension ref="A1:M652"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -1610,7 +1659,7 @@
     <col min="8" max="8" width="21" customWidth="1"/>
     <col min="9" max="9" width="19.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.85546875" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18821,7 +18870,7 @@
       <c r="H416" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I416" s="14">
+      <c r="I416" s="1">
         <v>26</v>
       </c>
       <c r="J416" s="1">
@@ -18864,7 +18913,7 @@
       <c r="H417" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="I417" s="14">
+      <c r="I417" s="1">
         <v>11</v>
       </c>
       <c r="J417" s="1">
@@ -18907,7 +18956,7 @@
       <c r="H418" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I418" s="14">
+      <c r="I418" s="1">
         <v>12</v>
       </c>
       <c r="J418" s="1">
@@ -20470,7 +20519,7 @@
       <c r="H454" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="I454" s="14">
+      <c r="I454" s="1">
         <v>18</v>
       </c>
       <c r="J454" s="1">
@@ -20513,7 +20562,7 @@
       <c r="H455" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I455" s="14">
+      <c r="I455" s="1">
         <v>6</v>
       </c>
       <c r="J455" s="1">
@@ -20556,7 +20605,7 @@
       <c r="H456" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="I456" s="14">
+      <c r="I456" s="1">
         <v>17</v>
       </c>
       <c r="J456" s="1">
@@ -21945,8 +21994,7108 @@
         <v>128</v>
       </c>
     </row>
+    <row r="489" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A489" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B489" s="1">
+        <v>4</v>
+      </c>
+      <c r="C489" t="s">
+        <v>97</v>
+      </c>
+      <c r="D489">
+        <f t="shared" ref="D489:D551" si="2">VLOOKUP(C489,$C$2:$D$352,2,0)</f>
+        <v>61</v>
+      </c>
+      <c r="E489" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F489" t="s">
+        <v>314</v>
+      </c>
+      <c r="G489" t="str">
+        <f>VLOOKUP(F489,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H489" t="s">
+        <v>92</v>
+      </c>
+      <c r="I489">
+        <f>VLOOKUP(H489,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>120</v>
+      </c>
+      <c r="J489" s="1">
+        <v>1</v>
+      </c>
+      <c r="K489">
+        <v>4</v>
+      </c>
+      <c r="L489" s="1">
+        <v>10</v>
+      </c>
+      <c r="M489" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="490" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A490" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B490" s="1">
+        <v>4</v>
+      </c>
+      <c r="C490" t="s">
+        <v>97</v>
+      </c>
+      <c r="D490">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E490" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F490" t="s">
+        <v>314</v>
+      </c>
+      <c r="G490" t="str">
+        <f>VLOOKUP(F490,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H490" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I490">
+        <f>VLOOKUP(H490,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>13</v>
+      </c>
+      <c r="J490" s="1">
+        <v>1</v>
+      </c>
+      <c r="K490">
+        <v>18</v>
+      </c>
+      <c r="L490" s="1">
+        <v>10</v>
+      </c>
+      <c r="M490" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="491" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A491" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B491" s="1">
+        <v>4</v>
+      </c>
+      <c r="C491" t="s">
+        <v>97</v>
+      </c>
+      <c r="D491">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E491" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F491" t="s">
+        <v>314</v>
+      </c>
+      <c r="G491" t="str">
+        <f>VLOOKUP(F491,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H491" t="s">
+        <v>83</v>
+      </c>
+      <c r="I491">
+        <f>VLOOKUP(H491,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>14</v>
+      </c>
+      <c r="J491" s="1">
+        <v>1</v>
+      </c>
+      <c r="K491">
+        <v>10</v>
+      </c>
+      <c r="L491" s="1">
+        <v>10</v>
+      </c>
+      <c r="M491" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="492" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A492" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B492" s="1">
+        <v>4</v>
+      </c>
+      <c r="C492" t="s">
+        <v>97</v>
+      </c>
+      <c r="D492">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E492" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F492" t="s">
+        <v>314</v>
+      </c>
+      <c r="G492" t="str">
+        <f>VLOOKUP(F492,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H492" t="s">
+        <v>18</v>
+      </c>
+      <c r="I492">
+        <f>VLOOKUP(H492,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>109</v>
+      </c>
+      <c r="J492" s="1">
+        <v>1</v>
+      </c>
+      <c r="K492">
+        <v>20</v>
+      </c>
+      <c r="L492" s="1">
+        <v>10</v>
+      </c>
+      <c r="M492" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="493" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A493" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B493" s="1">
+        <v>4</v>
+      </c>
+      <c r="C493" t="s">
+        <v>97</v>
+      </c>
+      <c r="D493">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E493" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F493" t="s">
+        <v>314</v>
+      </c>
+      <c r="G493" t="str">
+        <f>VLOOKUP(F493,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H493" t="s">
+        <v>131</v>
+      </c>
+      <c r="I493">
+        <f>VLOOKUP(H493,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>809</v>
+      </c>
+      <c r="J493" s="1">
+        <v>1</v>
+      </c>
+      <c r="K493">
+        <v>7</v>
+      </c>
+      <c r="L493" s="1">
+        <v>10</v>
+      </c>
+      <c r="M493" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="494" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A494" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B494" s="1">
+        <v>4</v>
+      </c>
+      <c r="C494" t="s">
+        <v>97</v>
+      </c>
+      <c r="D494">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E494" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F494" t="s">
+        <v>314</v>
+      </c>
+      <c r="G494" t="str">
+        <f>VLOOKUP(F494,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H494" t="s">
+        <v>23</v>
+      </c>
+      <c r="I494">
+        <f>VLOOKUP(H494,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>110</v>
+      </c>
+      <c r="J494" s="1">
+        <v>1</v>
+      </c>
+      <c r="L494" s="1">
+        <v>10</v>
+      </c>
+      <c r="M494" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="495" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A495" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B495" s="1">
+        <v>4</v>
+      </c>
+      <c r="C495" t="s">
+        <v>97</v>
+      </c>
+      <c r="D495">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E495" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F495" t="s">
+        <v>314</v>
+      </c>
+      <c r="G495" t="str">
+        <f>VLOOKUP(F495,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H495" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I495">
+        <f>VLOOKUP(H495,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>104</v>
+      </c>
+      <c r="J495" s="1">
+        <v>1</v>
+      </c>
+      <c r="K495">
+        <v>7</v>
+      </c>
+      <c r="L495" s="1">
+        <v>10</v>
+      </c>
+      <c r="M495" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="496" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A496" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B496" s="1">
+        <v>4</v>
+      </c>
+      <c r="C496" t="s">
+        <v>97</v>
+      </c>
+      <c r="D496">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E496" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F496" t="s">
+        <v>314</v>
+      </c>
+      <c r="G496" t="str">
+        <f>VLOOKUP(F496,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H496" t="s">
+        <v>263</v>
+      </c>
+      <c r="I496">
+        <f>VLOOKUP(H496,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>121</v>
+      </c>
+      <c r="J496" s="1">
+        <v>1</v>
+      </c>
+      <c r="L496" s="1">
+        <v>10</v>
+      </c>
+      <c r="M496" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="497" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A497" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B497" s="1">
+        <v>4</v>
+      </c>
+      <c r="C497" t="s">
+        <v>97</v>
+      </c>
+      <c r="D497">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E497" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F497" t="s">
+        <v>315</v>
+      </c>
+      <c r="G497" t="str">
+        <f>VLOOKUP(F497,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H497" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I497">
+        <f>VLOOKUP(H497,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>146</v>
+      </c>
+      <c r="J497" s="1">
+        <v>1</v>
+      </c>
+      <c r="K497">
+        <v>4</v>
+      </c>
+      <c r="L497" s="1">
+        <v>10</v>
+      </c>
+      <c r="M497" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="498" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A498" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B498" s="1">
+        <v>4</v>
+      </c>
+      <c r="C498" t="s">
+        <v>97</v>
+      </c>
+      <c r="D498">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E498" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F498" t="s">
+        <v>315</v>
+      </c>
+      <c r="G498" t="str">
+        <f>VLOOKUP(F498,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H498" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I498">
+        <f>VLOOKUP(H498,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>150</v>
+      </c>
+      <c r="J498" s="1">
+        <v>1</v>
+      </c>
+      <c r="K498">
+        <v>6</v>
+      </c>
+      <c r="L498" s="1">
+        <v>10</v>
+      </c>
+      <c r="M498" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="499" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A499" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B499" s="1">
+        <v>4</v>
+      </c>
+      <c r="C499" t="s">
+        <v>97</v>
+      </c>
+      <c r="D499">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E499" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F499" t="s">
+        <v>315</v>
+      </c>
+      <c r="G499" t="str">
+        <f>VLOOKUP(F499,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H499" t="s">
+        <v>74</v>
+      </c>
+      <c r="I499">
+        <f>VLOOKUP(H499,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>145</v>
+      </c>
+      <c r="J499" s="1">
+        <v>1</v>
+      </c>
+      <c r="K499">
+        <v>8</v>
+      </c>
+      <c r="L499" s="1">
+        <v>10</v>
+      </c>
+      <c r="M499" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="500" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A500" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B500" s="1">
+        <v>4</v>
+      </c>
+      <c r="C500" t="s">
+        <v>97</v>
+      </c>
+      <c r="D500">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E500" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F500" t="s">
+        <v>315</v>
+      </c>
+      <c r="G500" t="str">
+        <f>VLOOKUP(F500,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H500" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I500">
+        <f>VLOOKUP(H500,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>144</v>
+      </c>
+      <c r="J500" s="1">
+        <v>1</v>
+      </c>
+      <c r="K500">
+        <v>8</v>
+      </c>
+      <c r="L500" s="1">
+        <v>10</v>
+      </c>
+      <c r="M500" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="501" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A501" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B501" s="1">
+        <v>4</v>
+      </c>
+      <c r="C501" t="s">
+        <v>97</v>
+      </c>
+      <c r="D501">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E501" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F501" t="s">
+        <v>315</v>
+      </c>
+      <c r="G501" t="str">
+        <f>VLOOKUP(F501,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H501" t="s">
+        <v>84</v>
+      </c>
+      <c r="I501">
+        <f>VLOOKUP(H501,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>157</v>
+      </c>
+      <c r="J501" s="1">
+        <v>1</v>
+      </c>
+      <c r="K501">
+        <v>4</v>
+      </c>
+      <c r="L501" s="1">
+        <v>10</v>
+      </c>
+      <c r="M501" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="502" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A502" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B502" s="1">
+        <v>4</v>
+      </c>
+      <c r="C502" t="s">
+        <v>97</v>
+      </c>
+      <c r="D502">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E502" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F502" t="s">
+        <v>315</v>
+      </c>
+      <c r="G502" t="str">
+        <f>VLOOKUP(F502,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H502" t="s">
+        <v>85</v>
+      </c>
+      <c r="I502">
+        <f>VLOOKUP(H502,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>149</v>
+      </c>
+      <c r="J502" s="1">
+        <v>1</v>
+      </c>
+      <c r="K502">
+        <v>4</v>
+      </c>
+      <c r="L502" s="1">
+        <v>10</v>
+      </c>
+      <c r="M502" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="503" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A503" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B503" s="1">
+        <v>4</v>
+      </c>
+      <c r="C503" t="s">
+        <v>97</v>
+      </c>
+      <c r="D503">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E503" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F503" t="s">
+        <v>315</v>
+      </c>
+      <c r="G503" t="str">
+        <f>VLOOKUP(F503,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H503" t="s">
+        <v>86</v>
+      </c>
+      <c r="I503">
+        <f>VLOOKUP(H503,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>148</v>
+      </c>
+      <c r="J503" s="1">
+        <v>1</v>
+      </c>
+      <c r="K503">
+        <v>4</v>
+      </c>
+      <c r="L503" s="1">
+        <v>10</v>
+      </c>
+      <c r="M503" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="504" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A504" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B504" s="1">
+        <v>4</v>
+      </c>
+      <c r="C504" t="s">
+        <v>97</v>
+      </c>
+      <c r="D504">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E504" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F504" t="s">
+        <v>315</v>
+      </c>
+      <c r="G504" t="str">
+        <f>VLOOKUP(F504,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H504" t="s">
+        <v>87</v>
+      </c>
+      <c r="I504">
+        <f>VLOOKUP(H504,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>140</v>
+      </c>
+      <c r="J504" s="1">
+        <v>1</v>
+      </c>
+      <c r="K504">
+        <v>4</v>
+      </c>
+      <c r="L504" s="1">
+        <v>10</v>
+      </c>
+      <c r="M504" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="505" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A505" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B505" s="1">
+        <v>4</v>
+      </c>
+      <c r="C505" t="s">
+        <v>97</v>
+      </c>
+      <c r="D505">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E505" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F505" t="s">
+        <v>315</v>
+      </c>
+      <c r="G505" t="str">
+        <f>VLOOKUP(F505,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H505" t="s">
+        <v>77</v>
+      </c>
+      <c r="I505">
+        <f>VLOOKUP(H505,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>823</v>
+      </c>
+      <c r="J505" s="1">
+        <v>1</v>
+      </c>
+      <c r="K505">
+        <v>20</v>
+      </c>
+      <c r="L505" s="1">
+        <v>10</v>
+      </c>
+      <c r="M505" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="506" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A506" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B506" s="1">
+        <v>4</v>
+      </c>
+      <c r="C506" t="s">
+        <v>97</v>
+      </c>
+      <c r="D506">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E506" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F506" t="s">
+        <v>316</v>
+      </c>
+      <c r="G506" t="str">
+        <f>VLOOKUP(F506,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H506" t="s">
+        <v>48</v>
+      </c>
+      <c r="I506">
+        <f>VLOOKUP(H506,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>796</v>
+      </c>
+      <c r="J506" s="1">
+        <v>1</v>
+      </c>
+      <c r="K506">
+        <v>18</v>
+      </c>
+      <c r="L506" s="1">
+        <v>10</v>
+      </c>
+      <c r="M506" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="507" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A507" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B507" s="1">
+        <v>4</v>
+      </c>
+      <c r="C507" t="s">
+        <v>97</v>
+      </c>
+      <c r="D507">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E507" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F507" t="s">
+        <v>316</v>
+      </c>
+      <c r="G507" t="str">
+        <f>VLOOKUP(F507,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H507" t="s">
+        <v>50</v>
+      </c>
+      <c r="I507">
+        <f>VLOOKUP(H507,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>90</v>
+      </c>
+      <c r="J507" s="1">
+        <v>1</v>
+      </c>
+      <c r="K507">
+        <v>5</v>
+      </c>
+      <c r="L507" s="1">
+        <v>10</v>
+      </c>
+      <c r="M507" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="508" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A508" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B508" s="1">
+        <v>4</v>
+      </c>
+      <c r="C508" t="s">
+        <v>97</v>
+      </c>
+      <c r="D508">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E508" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F508" t="s">
+        <v>316</v>
+      </c>
+      <c r="G508" t="str">
+        <f>VLOOKUP(F508,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H508" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I508">
+        <f>VLOOKUP(H508,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>75</v>
+      </c>
+      <c r="J508" s="1">
+        <v>1</v>
+      </c>
+      <c r="K508">
+        <v>36</v>
+      </c>
+      <c r="L508" s="1">
+        <v>10</v>
+      </c>
+      <c r="M508" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="509" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A509" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B509" s="1">
+        <v>4</v>
+      </c>
+      <c r="C509" t="s">
+        <v>97</v>
+      </c>
+      <c r="D509">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E509" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F509" t="s">
+        <v>316</v>
+      </c>
+      <c r="G509" t="str">
+        <f>VLOOKUP(F509,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H509" t="s">
+        <v>49</v>
+      </c>
+      <c r="I509">
+        <f>VLOOKUP(H509,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>74</v>
+      </c>
+      <c r="J509" s="1">
+        <v>1</v>
+      </c>
+      <c r="K509">
+        <v>7</v>
+      </c>
+      <c r="L509" s="1">
+        <v>10</v>
+      </c>
+      <c r="M509" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="510" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A510" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B510" s="1">
+        <v>4</v>
+      </c>
+      <c r="C510" t="s">
+        <v>17</v>
+      </c>
+      <c r="D510">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E510" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F510" t="s">
+        <v>314</v>
+      </c>
+      <c r="G510" t="str">
+        <f>VLOOKUP(F510,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H510" t="s">
+        <v>18</v>
+      </c>
+      <c r="I510">
+        <f>VLOOKUP(H510,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>109</v>
+      </c>
+      <c r="J510" s="1">
+        <v>1</v>
+      </c>
+      <c r="K510">
+        <v>3</v>
+      </c>
+      <c r="L510" s="1">
+        <v>10</v>
+      </c>
+      <c r="M510" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="511" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A511" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B511" s="1">
+        <v>4</v>
+      </c>
+      <c r="C511" t="s">
+        <v>17</v>
+      </c>
+      <c r="D511">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E511" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F511" t="s">
+        <v>314</v>
+      </c>
+      <c r="G511" t="str">
+        <f>VLOOKUP(F511,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H511" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I511">
+        <f>VLOOKUP(H511,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>127</v>
+      </c>
+      <c r="J511" s="1">
+        <v>1</v>
+      </c>
+      <c r="K511">
+        <v>1</v>
+      </c>
+      <c r="L511" s="1">
+        <v>10</v>
+      </c>
+      <c r="M511" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="512" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A512" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B512" s="1">
+        <v>4</v>
+      </c>
+      <c r="C512" t="s">
+        <v>17</v>
+      </c>
+      <c r="D512">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E512" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F512" t="s">
+        <v>314</v>
+      </c>
+      <c r="G512" t="str">
+        <f>VLOOKUP(F512,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H512" t="s">
+        <v>21</v>
+      </c>
+      <c r="I512">
+        <f>VLOOKUP(H512,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>884</v>
+      </c>
+      <c r="J512" s="1">
+        <v>1</v>
+      </c>
+      <c r="K512">
+        <v>1</v>
+      </c>
+      <c r="L512" s="1">
+        <v>10</v>
+      </c>
+      <c r="M512" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="513" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A513" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B513" s="1">
+        <v>4</v>
+      </c>
+      <c r="C513" t="s">
+        <v>17</v>
+      </c>
+      <c r="D513">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E513" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F513" t="s">
+        <v>314</v>
+      </c>
+      <c r="G513" t="str">
+        <f>VLOOKUP(F513,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H513" t="s">
+        <v>263</v>
+      </c>
+      <c r="I513">
+        <f>VLOOKUP(H513,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>121</v>
+      </c>
+      <c r="J513" s="1">
+        <v>1</v>
+      </c>
+      <c r="K513">
+        <v>2</v>
+      </c>
+      <c r="L513" s="1">
+        <v>10</v>
+      </c>
+      <c r="M513" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="514" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A514" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B514" s="1">
+        <v>4</v>
+      </c>
+      <c r="C514" t="s">
+        <v>17</v>
+      </c>
+      <c r="D514">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E514" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F514" t="s">
+        <v>314</v>
+      </c>
+      <c r="G514" t="str">
+        <f>VLOOKUP(F514,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H514" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="I514">
+        <f>VLOOKUP(H514,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>103</v>
+      </c>
+      <c r="J514" s="1">
+        <v>1</v>
+      </c>
+      <c r="L514" s="1">
+        <v>10</v>
+      </c>
+      <c r="M514" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="515" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A515" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B515" s="1">
+        <v>4</v>
+      </c>
+      <c r="C515" t="s">
+        <v>17</v>
+      </c>
+      <c r="D515">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E515" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F515" t="s">
+        <v>314</v>
+      </c>
+      <c r="G515" t="str">
+        <f>VLOOKUP(F515,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H515" t="s">
+        <v>320</v>
+      </c>
+      <c r="I515">
+        <f>VLOOKUP(H515,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>110</v>
+      </c>
+      <c r="J515" s="1">
+        <v>1</v>
+      </c>
+      <c r="K515">
+        <v>2</v>
+      </c>
+      <c r="L515" s="1">
+        <v>10</v>
+      </c>
+      <c r="M515" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="516" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A516" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B516" s="1">
+        <v>4</v>
+      </c>
+      <c r="C516" t="s">
+        <v>17</v>
+      </c>
+      <c r="D516">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E516" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F516" t="s">
+        <v>317</v>
+      </c>
+      <c r="G516" t="str">
+        <f>VLOOKUP(F516,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H516" t="s">
+        <v>120</v>
+      </c>
+      <c r="I516">
+        <f>VLOOKUP(H516,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>11</v>
+      </c>
+      <c r="J516" s="1">
+        <v>1</v>
+      </c>
+      <c r="K516">
+        <v>5</v>
+      </c>
+      <c r="L516" s="1">
+        <v>10</v>
+      </c>
+      <c r="M516" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="517" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A517" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B517" s="1">
+        <v>4</v>
+      </c>
+      <c r="C517" t="s">
+        <v>17</v>
+      </c>
+      <c r="D517">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E517" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F517" t="s">
+        <v>317</v>
+      </c>
+      <c r="G517" t="str">
+        <f>VLOOKUP(F517,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H517" t="s">
+        <v>25</v>
+      </c>
+      <c r="I517">
+        <f>VLOOKUP(H517,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>26</v>
+      </c>
+      <c r="J517" s="1">
+        <v>1</v>
+      </c>
+      <c r="L517" s="1">
+        <v>10</v>
+      </c>
+      <c r="M517" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A518" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B518" s="1">
+        <v>4</v>
+      </c>
+      <c r="C518" t="s">
+        <v>17</v>
+      </c>
+      <c r="D518">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E518" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F518" t="s">
+        <v>317</v>
+      </c>
+      <c r="G518" t="str">
+        <f>VLOOKUP(F518,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H518" t="s">
+        <v>27</v>
+      </c>
+      <c r="I518">
+        <f>VLOOKUP(H518,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>12</v>
+      </c>
+      <c r="J518" s="1">
+        <v>1</v>
+      </c>
+      <c r="K518">
+        <v>4</v>
+      </c>
+      <c r="L518" s="1">
+        <v>10</v>
+      </c>
+      <c r="M518" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="519" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A519" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B519" s="1">
+        <v>4</v>
+      </c>
+      <c r="C519" t="s">
+        <v>17</v>
+      </c>
+      <c r="D519">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E519" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F519" t="s">
+        <v>318</v>
+      </c>
+      <c r="G519" t="str">
+        <f>VLOOKUP(F519,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H519" t="s">
+        <v>16</v>
+      </c>
+      <c r="I519">
+        <f>VLOOKUP(H519,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="J519" s="1">
+        <v>1</v>
+      </c>
+      <c r="K519">
+        <v>4</v>
+      </c>
+      <c r="L519" s="1">
+        <v>10</v>
+      </c>
+      <c r="M519" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="520" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A520" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B520" s="1">
+        <v>4</v>
+      </c>
+      <c r="C520" t="s">
+        <v>17</v>
+      </c>
+      <c r="D520">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E520" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F520" t="s">
+        <v>318</v>
+      </c>
+      <c r="G520" t="str">
+        <f>VLOOKUP(F520,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H520" t="s">
+        <v>28</v>
+      </c>
+      <c r="I520">
+        <f>VLOOKUP(H520,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>1</v>
+      </c>
+      <c r="J520" s="1">
+        <v>1</v>
+      </c>
+      <c r="K520">
+        <v>3</v>
+      </c>
+      <c r="L520" s="1">
+        <v>10</v>
+      </c>
+      <c r="M520" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="521" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A521" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B521" s="1">
+        <v>4</v>
+      </c>
+      <c r="C521" t="s">
+        <v>17</v>
+      </c>
+      <c r="D521">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E521" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F521" t="s">
+        <v>318</v>
+      </c>
+      <c r="G521" t="str">
+        <f>VLOOKUP(F521,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H521" t="s">
+        <v>31</v>
+      </c>
+      <c r="I521">
+        <f>VLOOKUP(H521,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>30</v>
+      </c>
+      <c r="J521" s="1">
+        <v>1</v>
+      </c>
+      <c r="K521">
+        <v>2</v>
+      </c>
+      <c r="L521" s="1">
+        <v>10</v>
+      </c>
+      <c r="M521" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="522" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A522" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B522" s="1">
+        <v>4</v>
+      </c>
+      <c r="C522" t="s">
+        <v>95</v>
+      </c>
+      <c r="D522">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E522" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F522" t="s">
+        <v>316</v>
+      </c>
+      <c r="G522" t="str">
+        <f>VLOOKUP(F522,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H522" t="s">
+        <v>49</v>
+      </c>
+      <c r="I522">
+        <f>VLOOKUP(H522,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>74</v>
+      </c>
+      <c r="J522" s="1">
+        <v>1</v>
+      </c>
+      <c r="K522">
+        <v>4</v>
+      </c>
+      <c r="L522" s="1">
+        <v>10</v>
+      </c>
+      <c r="M522" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="523" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A523" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B523" s="1">
+        <v>4</v>
+      </c>
+      <c r="C523" t="s">
+        <v>95</v>
+      </c>
+      <c r="D523">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E523" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F523" t="s">
+        <v>316</v>
+      </c>
+      <c r="G523" t="str">
+        <f>VLOOKUP(F523,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H523" t="s">
+        <v>51</v>
+      </c>
+      <c r="I523">
+        <f>VLOOKUP(H523,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>75</v>
+      </c>
+      <c r="J523" s="1">
+        <v>1</v>
+      </c>
+      <c r="K523">
+        <v>13</v>
+      </c>
+      <c r="L523" s="1">
+        <v>10</v>
+      </c>
+      <c r="M523" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="524" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A524" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B524" s="1">
+        <v>4</v>
+      </c>
+      <c r="C524" t="s">
+        <v>95</v>
+      </c>
+      <c r="D524">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E524" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F524" t="s">
+        <v>316</v>
+      </c>
+      <c r="G524" t="str">
+        <f>VLOOKUP(F524,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H524" t="s">
+        <v>48</v>
+      </c>
+      <c r="I524">
+        <f>VLOOKUP(H524,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>796</v>
+      </c>
+      <c r="J524" s="1">
+        <v>1</v>
+      </c>
+      <c r="K524">
+        <v>2</v>
+      </c>
+      <c r="L524" s="1">
+        <v>10</v>
+      </c>
+      <c r="M524" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="525" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A525" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B525" s="1">
+        <v>4</v>
+      </c>
+      <c r="C525" t="s">
+        <v>95</v>
+      </c>
+      <c r="D525">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E525" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F525" t="s">
+        <v>316</v>
+      </c>
+      <c r="G525" t="str">
+        <f>VLOOKUP(F525,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H525" t="s">
+        <v>321</v>
+      </c>
+      <c r="I525">
+        <f>VLOOKUP(H525,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>90</v>
+      </c>
+      <c r="J525" s="1">
+        <v>1</v>
+      </c>
+      <c r="K525">
+        <v>0</v>
+      </c>
+      <c r="L525" s="1">
+        <v>10</v>
+      </c>
+      <c r="M525" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="526" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A526" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B526" s="1">
+        <v>4</v>
+      </c>
+      <c r="C526" t="s">
+        <v>95</v>
+      </c>
+      <c r="D526">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E526" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F526" t="s">
+        <v>317</v>
+      </c>
+      <c r="G526" t="str">
+        <f>VLOOKUP(F526,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H526" t="s">
+        <v>38</v>
+      </c>
+      <c r="I526">
+        <f>VLOOKUP(H526,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>12</v>
+      </c>
+      <c r="J526" s="1">
+        <v>1</v>
+      </c>
+      <c r="K526">
+        <v>19</v>
+      </c>
+      <c r="L526" s="1">
+        <v>10</v>
+      </c>
+      <c r="M526" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="527" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A527" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B527" s="1">
+        <v>4</v>
+      </c>
+      <c r="C527" t="s">
+        <v>95</v>
+      </c>
+      <c r="D527">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E527" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F527" t="s">
+        <v>317</v>
+      </c>
+      <c r="G527" t="str">
+        <f>VLOOKUP(F527,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H527" t="s">
+        <v>120</v>
+      </c>
+      <c r="I527">
+        <f>VLOOKUP(H527,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>11</v>
+      </c>
+      <c r="J527" s="1">
+        <v>1</v>
+      </c>
+      <c r="K527">
+        <v>0</v>
+      </c>
+      <c r="L527" s="1">
+        <v>10</v>
+      </c>
+      <c r="M527" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="528" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A528" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B528" s="1">
+        <v>4</v>
+      </c>
+      <c r="C528" t="s">
+        <v>95</v>
+      </c>
+      <c r="D528">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E528" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F528" t="s">
+        <v>317</v>
+      </c>
+      <c r="G528" t="str">
+        <f>VLOOKUP(F528,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H528" t="s">
+        <v>121</v>
+      </c>
+      <c r="I528">
+        <f>VLOOKUP(H528,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>29</v>
+      </c>
+      <c r="J528" s="1">
+        <v>1</v>
+      </c>
+      <c r="K528">
+        <v>0</v>
+      </c>
+      <c r="L528" s="1">
+        <v>10</v>
+      </c>
+      <c r="M528" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="529" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A529" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B529" s="1">
+        <v>4</v>
+      </c>
+      <c r="C529" t="s">
+        <v>95</v>
+      </c>
+      <c r="D529">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E529" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F529" t="s">
+        <v>317</v>
+      </c>
+      <c r="G529" t="str">
+        <f>VLOOKUP(F529,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H529" t="s">
+        <v>300</v>
+      </c>
+      <c r="I529">
+        <f>VLOOKUP(H529,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>820</v>
+      </c>
+      <c r="J529" s="1">
+        <v>1</v>
+      </c>
+      <c r="K529">
+        <v>0</v>
+      </c>
+      <c r="L529" s="1">
+        <v>10</v>
+      </c>
+      <c r="M529" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="530" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A530" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B530" s="1">
+        <v>4</v>
+      </c>
+      <c r="C530" t="s">
+        <v>95</v>
+      </c>
+      <c r="D530">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E530" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F530" t="s">
+        <v>130</v>
+      </c>
+      <c r="G530" t="str">
+        <f>VLOOKUP(F530,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H530" t="s">
+        <v>53</v>
+      </c>
+      <c r="I530">
+        <f>VLOOKUP(H530,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>794</v>
+      </c>
+      <c r="J530" s="1">
+        <v>1</v>
+      </c>
+      <c r="K530">
+        <v>12</v>
+      </c>
+      <c r="L530" s="1">
+        <v>10</v>
+      </c>
+      <c r="M530" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="531" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A531" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B531" s="1">
+        <v>4</v>
+      </c>
+      <c r="C531" t="s">
+        <v>95</v>
+      </c>
+      <c r="D531">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E531" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F531" t="s">
+        <v>130</v>
+      </c>
+      <c r="G531" t="str">
+        <f>VLOOKUP(F531,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H531" t="s">
+        <v>54</v>
+      </c>
+      <c r="I531">
+        <f>VLOOKUP(H531,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>815</v>
+      </c>
+      <c r="J531" s="1">
+        <v>1</v>
+      </c>
+      <c r="K531">
+        <v>3</v>
+      </c>
+      <c r="L531" s="1">
+        <v>10</v>
+      </c>
+      <c r="M531" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="532" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A532" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B532" s="1">
+        <v>4</v>
+      </c>
+      <c r="C532" t="s">
+        <v>95</v>
+      </c>
+      <c r="D532">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E532" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F532" t="s">
+        <v>130</v>
+      </c>
+      <c r="G532" t="str">
+        <f>VLOOKUP(F532,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H532" t="s">
+        <v>55</v>
+      </c>
+      <c r="I532">
+        <f>VLOOKUP(H532,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>795</v>
+      </c>
+      <c r="J532" s="1">
+        <v>1</v>
+      </c>
+      <c r="K532">
+        <v>4</v>
+      </c>
+      <c r="L532" s="1">
+        <v>10</v>
+      </c>
+      <c r="M532" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="533" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A533" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B533" s="1">
+        <v>4</v>
+      </c>
+      <c r="C533" t="s">
+        <v>95</v>
+      </c>
+      <c r="D533">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E533" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F533" t="s">
+        <v>130</v>
+      </c>
+      <c r="G533" t="str">
+        <f>VLOOKUP(F533,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H533" t="s">
+        <v>12</v>
+      </c>
+      <c r="I533">
+        <f>VLOOKUP(H533,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>23</v>
+      </c>
+      <c r="J533" s="1">
+        <v>1</v>
+      </c>
+      <c r="K533">
+        <v>0</v>
+      </c>
+      <c r="L533" s="1">
+        <v>10</v>
+      </c>
+      <c r="M533" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="534" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A534" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B534" s="1">
+        <v>4</v>
+      </c>
+      <c r="C534" t="s">
+        <v>6</v>
+      </c>
+      <c r="D534">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="E534" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F534" t="s">
+        <v>314</v>
+      </c>
+      <c r="G534" t="str">
+        <f>VLOOKUP(F534,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H534" t="s">
+        <v>18</v>
+      </c>
+      <c r="I534">
+        <f>VLOOKUP(H534,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>109</v>
+      </c>
+      <c r="J534" s="1">
+        <v>1</v>
+      </c>
+      <c r="K534">
+        <v>2</v>
+      </c>
+      <c r="L534" s="1">
+        <v>10</v>
+      </c>
+      <c r="M534" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="535" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A535" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B535" s="1">
+        <v>4</v>
+      </c>
+      <c r="C535" t="s">
+        <v>6</v>
+      </c>
+      <c r="D535">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="E535" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F535" t="s">
+        <v>314</v>
+      </c>
+      <c r="G535" t="str">
+        <f>VLOOKUP(F535,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H535" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="I535">
+        <f>VLOOKUP(H535,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>103</v>
+      </c>
+      <c r="J535" s="1">
+        <v>1</v>
+      </c>
+      <c r="L535" s="1">
+        <v>10</v>
+      </c>
+      <c r="M535" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="536" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A536" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B536" s="1">
+        <v>4</v>
+      </c>
+      <c r="C536" t="s">
+        <v>6</v>
+      </c>
+      <c r="D536">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="E536" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F536" t="s">
+        <v>314</v>
+      </c>
+      <c r="G536" t="str">
+        <f>VLOOKUP(F536,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H536" t="s">
+        <v>23</v>
+      </c>
+      <c r="I536">
+        <f>VLOOKUP(H536,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>110</v>
+      </c>
+      <c r="J536" s="1">
+        <v>1</v>
+      </c>
+      <c r="L536" s="1">
+        <v>10</v>
+      </c>
+      <c r="M536" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="537" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A537" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B537" s="1">
+        <v>4</v>
+      </c>
+      <c r="C537" t="s">
+        <v>6</v>
+      </c>
+      <c r="D537">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="E537" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F537" t="s">
+        <v>314</v>
+      </c>
+      <c r="G537" t="str">
+        <f>VLOOKUP(F537,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H537" t="s">
+        <v>261</v>
+      </c>
+      <c r="I537">
+        <f>VLOOKUP(H537,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>117</v>
+      </c>
+      <c r="J537" s="1">
+        <v>1</v>
+      </c>
+      <c r="K537">
+        <v>2</v>
+      </c>
+      <c r="L537" s="1">
+        <v>10</v>
+      </c>
+      <c r="M537" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="538" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A538" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B538" s="1">
+        <v>4</v>
+      </c>
+      <c r="C538" t="s">
+        <v>6</v>
+      </c>
+      <c r="D538">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="E538" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F538" t="s">
+        <v>314</v>
+      </c>
+      <c r="G538" t="str">
+        <f>VLOOKUP(F538,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H538" t="s">
+        <v>9</v>
+      </c>
+      <c r="I538">
+        <f>VLOOKUP(H538,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>118</v>
+      </c>
+      <c r="J538" s="1">
+        <v>1</v>
+      </c>
+      <c r="K538">
+        <v>2</v>
+      </c>
+      <c r="L538" s="1">
+        <v>10</v>
+      </c>
+      <c r="M538" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="539" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A539" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B539" s="1">
+        <v>4</v>
+      </c>
+      <c r="C539" t="s">
+        <v>29</v>
+      </c>
+      <c r="D539">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="E539" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F539" t="s">
+        <v>314</v>
+      </c>
+      <c r="G539" t="str">
+        <f>VLOOKUP(F539,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H539" t="s">
+        <v>18</v>
+      </c>
+      <c r="I539">
+        <f>VLOOKUP(H539,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>109</v>
+      </c>
+      <c r="J539" s="1">
+        <v>1</v>
+      </c>
+      <c r="K539">
+        <v>4</v>
+      </c>
+      <c r="L539" s="1">
+        <v>10</v>
+      </c>
+      <c r="M539" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="540" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A540" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B540" s="1">
+        <v>4</v>
+      </c>
+      <c r="C540" t="s">
+        <v>29</v>
+      </c>
+      <c r="D540">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="E540" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F540" t="s">
+        <v>314</v>
+      </c>
+      <c r="G540" t="str">
+        <f>VLOOKUP(F540,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H540" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="I540">
+        <f>VLOOKUP(H540,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>103</v>
+      </c>
+      <c r="J540" s="1">
+        <v>1</v>
+      </c>
+      <c r="K540">
+        <v>1</v>
+      </c>
+      <c r="L540" s="1">
+        <v>10</v>
+      </c>
+      <c r="M540" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="541" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A541" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B541" s="1">
+        <v>4</v>
+      </c>
+      <c r="C541" t="s">
+        <v>29</v>
+      </c>
+      <c r="D541">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="E541" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F541" t="s">
+        <v>314</v>
+      </c>
+      <c r="G541" t="str">
+        <f>VLOOKUP(F541,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H541" t="s">
+        <v>23</v>
+      </c>
+      <c r="I541">
+        <f>VLOOKUP(H541,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>110</v>
+      </c>
+      <c r="J541" s="1">
+        <v>1</v>
+      </c>
+      <c r="K541">
+        <v>4</v>
+      </c>
+      <c r="L541" s="1">
+        <v>10</v>
+      </c>
+      <c r="M541" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="542" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A542" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B542" s="1">
+        <v>4</v>
+      </c>
+      <c r="C542" t="s">
+        <v>29</v>
+      </c>
+      <c r="D542">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="E542" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F542" t="s">
+        <v>314</v>
+      </c>
+      <c r="G542" t="str">
+        <f>VLOOKUP(F542,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H542" t="s">
+        <v>261</v>
+      </c>
+      <c r="I542">
+        <f>VLOOKUP(H542,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>117</v>
+      </c>
+      <c r="J542" s="1">
+        <v>1</v>
+      </c>
+      <c r="L542" s="1">
+        <v>10</v>
+      </c>
+      <c r="M542" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="543" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A543" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B543" s="1">
+        <v>4</v>
+      </c>
+      <c r="C543" t="s">
+        <v>29</v>
+      </c>
+      <c r="D543">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="E543" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F543" t="s">
+        <v>314</v>
+      </c>
+      <c r="G543" t="str">
+        <f>VLOOKUP(F543,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H543" t="s">
+        <v>9</v>
+      </c>
+      <c r="I543">
+        <f>VLOOKUP(H543,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>118</v>
+      </c>
+      <c r="J543" s="1">
+        <v>1</v>
+      </c>
+      <c r="K543">
+        <v>2</v>
+      </c>
+      <c r="L543" s="1">
+        <v>10</v>
+      </c>
+      <c r="M543" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="544" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A544" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B544" s="1">
+        <v>4</v>
+      </c>
+      <c r="C544" t="s">
+        <v>6</v>
+      </c>
+      <c r="D544">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="E544" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F544" t="s">
+        <v>130</v>
+      </c>
+      <c r="G544" t="str">
+        <f>VLOOKUP(F544,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H544" t="s">
+        <v>54</v>
+      </c>
+      <c r="I544">
+        <f>VLOOKUP(H544,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>815</v>
+      </c>
+      <c r="J544" s="1">
+        <v>1</v>
+      </c>
+      <c r="L544" s="1">
+        <v>10</v>
+      </c>
+      <c r="M544" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="545" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A545" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B545" s="1">
+        <v>4</v>
+      </c>
+      <c r="C545" t="s">
+        <v>6</v>
+      </c>
+      <c r="D545">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="E545" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F545" t="s">
+        <v>130</v>
+      </c>
+      <c r="G545" t="str">
+        <f>VLOOKUP(F545,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H545" t="s">
+        <v>13</v>
+      </c>
+      <c r="I545">
+        <f>VLOOKUP(H545,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>794</v>
+      </c>
+      <c r="J545" s="1">
+        <v>1</v>
+      </c>
+      <c r="K545">
+        <v>4</v>
+      </c>
+      <c r="L545" s="1">
+        <v>10</v>
+      </c>
+      <c r="M545" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="546" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A546" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B546" s="1">
+        <v>4</v>
+      </c>
+      <c r="C546" t="s">
+        <v>6</v>
+      </c>
+      <c r="D546">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="E546" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F546" t="s">
+        <v>130</v>
+      </c>
+      <c r="G546" t="str">
+        <f>VLOOKUP(F546,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H546" t="s">
+        <v>30</v>
+      </c>
+      <c r="I546">
+        <f>VLOOKUP(H546,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>795</v>
+      </c>
+      <c r="J546" s="1">
+        <v>1</v>
+      </c>
+      <c r="K546">
+        <v>2</v>
+      </c>
+      <c r="L546" s="1">
+        <v>10</v>
+      </c>
+      <c r="M546" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="547" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A547" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B547" s="1">
+        <v>4</v>
+      </c>
+      <c r="C547" t="s">
+        <v>29</v>
+      </c>
+      <c r="D547">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="E547" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F547" t="s">
+        <v>130</v>
+      </c>
+      <c r="G547" t="str">
+        <f>VLOOKUP(F547,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H547" t="s">
+        <v>54</v>
+      </c>
+      <c r="I547">
+        <f>VLOOKUP(H547,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>815</v>
+      </c>
+      <c r="J547" s="1">
+        <v>1</v>
+      </c>
+      <c r="K547">
+        <v>2</v>
+      </c>
+      <c r="L547" s="1">
+        <v>10</v>
+      </c>
+      <c r="M547" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="548" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A548" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B548" s="1">
+        <v>4</v>
+      </c>
+      <c r="C548" t="s">
+        <v>29</v>
+      </c>
+      <c r="D548">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="E548" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F548" t="s">
+        <v>130</v>
+      </c>
+      <c r="G548" t="str">
+        <f>VLOOKUP(F548,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H548" t="s">
+        <v>13</v>
+      </c>
+      <c r="I548">
+        <f>VLOOKUP(H548,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>794</v>
+      </c>
+      <c r="J548" s="1">
+        <v>1</v>
+      </c>
+      <c r="K548">
+        <v>5</v>
+      </c>
+      <c r="L548" s="1">
+        <v>10</v>
+      </c>
+      <c r="M548" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="549" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A549" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B549" s="1">
+        <v>4</v>
+      </c>
+      <c r="C549" t="s">
+        <v>29</v>
+      </c>
+      <c r="D549">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="E549" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F549" t="s">
+        <v>130</v>
+      </c>
+      <c r="G549" t="str">
+        <f>VLOOKUP(F549,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H549" t="s">
+        <v>30</v>
+      </c>
+      <c r="I549">
+        <f>VLOOKUP(H549,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>795</v>
+      </c>
+      <c r="J549" s="1">
+        <v>1</v>
+      </c>
+      <c r="K549">
+        <v>4</v>
+      </c>
+      <c r="L549" s="1">
+        <v>10</v>
+      </c>
+      <c r="M549" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="550" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A550" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B550" s="1">
+        <v>4</v>
+      </c>
+      <c r="C550" t="s">
+        <v>6</v>
+      </c>
+      <c r="D550">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="E550" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F550" t="s">
+        <v>318</v>
+      </c>
+      <c r="G550" t="str">
+        <f>VLOOKUP(F550,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H550" t="s">
+        <v>56</v>
+      </c>
+      <c r="I550">
+        <f>VLOOKUP(H550,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>32</v>
+      </c>
+      <c r="J550" s="1">
+        <v>1</v>
+      </c>
+      <c r="K550">
+        <v>0</v>
+      </c>
+      <c r="L550" s="1">
+        <v>10</v>
+      </c>
+      <c r="M550" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="551" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A551" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B551" s="1">
+        <v>4</v>
+      </c>
+      <c r="C551" t="s">
+        <v>6</v>
+      </c>
+      <c r="D551">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="E551" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F551" t="s">
+        <v>318</v>
+      </c>
+      <c r="G551" t="str">
+        <f>VLOOKUP(F551,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H551" t="s">
+        <v>16</v>
+      </c>
+      <c r="I551">
+        <f>VLOOKUP(H551,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="J551" s="1">
+        <v>1</v>
+      </c>
+      <c r="K551">
+        <v>6</v>
+      </c>
+      <c r="L551" s="1">
+        <v>10</v>
+      </c>
+      <c r="M551" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="552" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A552" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B552" s="1">
+        <v>4</v>
+      </c>
+      <c r="C552" t="s">
+        <v>6</v>
+      </c>
+      <c r="D552">
+        <f t="shared" ref="D552:D614" si="3">VLOOKUP(C552,$C$2:$D$352,2,0)</f>
+        <v>102</v>
+      </c>
+      <c r="E552" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F552" t="s">
+        <v>318</v>
+      </c>
+      <c r="G552" t="str">
+        <f>VLOOKUP(F552,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H552" t="s">
+        <v>28</v>
+      </c>
+      <c r="I552">
+        <f>VLOOKUP(H552,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>1</v>
+      </c>
+      <c r="J552" s="1">
+        <v>1</v>
+      </c>
+      <c r="K552">
+        <v>0</v>
+      </c>
+      <c r="L552" s="1">
+        <v>10</v>
+      </c>
+      <c r="M552" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="553" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A553" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B553" s="1">
+        <v>4</v>
+      </c>
+      <c r="C553" t="s">
+        <v>6</v>
+      </c>
+      <c r="D553">
+        <f t="shared" si="3"/>
+        <v>102</v>
+      </c>
+      <c r="E553" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F553" t="s">
+        <v>318</v>
+      </c>
+      <c r="G553" t="str">
+        <f>VLOOKUP(F553,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H553" t="s">
+        <v>31</v>
+      </c>
+      <c r="I553">
+        <f>VLOOKUP(H553,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>30</v>
+      </c>
+      <c r="J553" s="1">
+        <v>1</v>
+      </c>
+      <c r="K553">
+        <v>0</v>
+      </c>
+      <c r="L553" s="1">
+        <v>10</v>
+      </c>
+      <c r="M553" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="554" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A554" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B554" s="1">
+        <v>4</v>
+      </c>
+      <c r="C554" t="s">
+        <v>6</v>
+      </c>
+      <c r="D554">
+        <f t="shared" si="3"/>
+        <v>102</v>
+      </c>
+      <c r="E554" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F554" t="s">
+        <v>318</v>
+      </c>
+      <c r="G554" t="str">
+        <f>VLOOKUP(F554,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H554" t="s">
+        <v>46</v>
+      </c>
+      <c r="I554">
+        <f>VLOOKUP(H554,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>57</v>
+      </c>
+      <c r="J554" s="1">
+        <v>1</v>
+      </c>
+      <c r="L554" s="1">
+        <v>10</v>
+      </c>
+      <c r="M554" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="555" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A555" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B555" s="1">
+        <v>4</v>
+      </c>
+      <c r="C555" t="s">
+        <v>6</v>
+      </c>
+      <c r="D555">
+        <f t="shared" si="3"/>
+        <v>102</v>
+      </c>
+      <c r="E555" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F555" t="s">
+        <v>318</v>
+      </c>
+      <c r="G555" t="str">
+        <f>VLOOKUP(F555,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H555" t="s">
+        <v>45</v>
+      </c>
+      <c r="I555">
+        <f>VLOOKUP(H555,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>33</v>
+      </c>
+      <c r="J555" s="1">
+        <v>1</v>
+      </c>
+      <c r="K555">
+        <v>0</v>
+      </c>
+      <c r="L555" s="1">
+        <v>10</v>
+      </c>
+      <c r="M555" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="556" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A556" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B556" s="1">
+        <v>4</v>
+      </c>
+      <c r="C556" t="s">
+        <v>29</v>
+      </c>
+      <c r="D556">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="E556" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F556" t="s">
+        <v>318</v>
+      </c>
+      <c r="G556" t="str">
+        <f>VLOOKUP(F556,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H556" t="s">
+        <v>56</v>
+      </c>
+      <c r="I556">
+        <f>VLOOKUP(H556,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>32</v>
+      </c>
+      <c r="J556" s="1">
+        <v>1</v>
+      </c>
+      <c r="L556" s="1">
+        <v>10</v>
+      </c>
+      <c r="M556" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="557" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A557" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B557" s="1">
+        <v>4</v>
+      </c>
+      <c r="C557" t="s">
+        <v>29</v>
+      </c>
+      <c r="D557">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="E557" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F557" t="s">
+        <v>318</v>
+      </c>
+      <c r="G557" t="str">
+        <f>VLOOKUP(F557,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H557" t="s">
+        <v>16</v>
+      </c>
+      <c r="I557">
+        <f>VLOOKUP(H557,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="J557" s="1">
+        <v>1</v>
+      </c>
+      <c r="K557">
+        <v>6</v>
+      </c>
+      <c r="L557" s="1">
+        <v>10</v>
+      </c>
+      <c r="M557" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="558" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A558" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B558" s="1">
+        <v>4</v>
+      </c>
+      <c r="C558" t="s">
+        <v>29</v>
+      </c>
+      <c r="D558">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="E558" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F558" t="s">
+        <v>318</v>
+      </c>
+      <c r="G558" t="str">
+        <f>VLOOKUP(F558,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H558" t="s">
+        <v>28</v>
+      </c>
+      <c r="I558">
+        <f>VLOOKUP(H558,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>1</v>
+      </c>
+      <c r="J558" s="1">
+        <v>1</v>
+      </c>
+      <c r="L558" s="1">
+        <v>10</v>
+      </c>
+      <c r="M558" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="559" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A559" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B559" s="1">
+        <v>4</v>
+      </c>
+      <c r="C559" t="s">
+        <v>29</v>
+      </c>
+      <c r="D559">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="E559" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F559" t="s">
+        <v>318</v>
+      </c>
+      <c r="G559" t="str">
+        <f>VLOOKUP(F559,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H559" t="s">
+        <v>31</v>
+      </c>
+      <c r="I559">
+        <f>VLOOKUP(H559,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>30</v>
+      </c>
+      <c r="J559" s="1">
+        <v>1</v>
+      </c>
+      <c r="K559">
+        <v>2</v>
+      </c>
+      <c r="L559" s="1">
+        <v>10</v>
+      </c>
+      <c r="M559" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="560" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A560" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B560" s="1">
+        <v>4</v>
+      </c>
+      <c r="C560" t="s">
+        <v>29</v>
+      </c>
+      <c r="D560">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="E560" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F560" t="s">
+        <v>318</v>
+      </c>
+      <c r="G560" t="str">
+        <f>VLOOKUP(F560,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H560" t="s">
+        <v>46</v>
+      </c>
+      <c r="I560">
+        <f>VLOOKUP(H560,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>57</v>
+      </c>
+      <c r="J560" s="1">
+        <v>1</v>
+      </c>
+      <c r="K560">
+        <v>2</v>
+      </c>
+      <c r="L560" s="1">
+        <v>10</v>
+      </c>
+      <c r="M560" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="561" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A561" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B561" s="1">
+        <v>4</v>
+      </c>
+      <c r="C561" t="s">
+        <v>29</v>
+      </c>
+      <c r="D561">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="E561" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F561" t="s">
+        <v>318</v>
+      </c>
+      <c r="G561" t="str">
+        <f>VLOOKUP(F561,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H561" t="s">
+        <v>45</v>
+      </c>
+      <c r="I561">
+        <f>VLOOKUP(H561,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>33</v>
+      </c>
+      <c r="J561" s="1">
+        <v>1</v>
+      </c>
+      <c r="K561">
+        <v>1</v>
+      </c>
+      <c r="L561" s="1">
+        <v>10</v>
+      </c>
+      <c r="M561" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="562" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A562" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B562" s="1">
+        <v>4</v>
+      </c>
+      <c r="C562" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D562">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E562" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F562" t="s">
+        <v>315</v>
+      </c>
+      <c r="G562" t="str">
+        <f>VLOOKUP(F562,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H562" t="s">
+        <v>77</v>
+      </c>
+      <c r="I562">
+        <f>VLOOKUP(H562,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>823</v>
+      </c>
+      <c r="J562" s="1">
+        <v>1</v>
+      </c>
+      <c r="K562">
+        <v>3</v>
+      </c>
+      <c r="L562" s="1">
+        <v>10</v>
+      </c>
+      <c r="M562" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="563" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A563" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B563" s="1">
+        <v>4</v>
+      </c>
+      <c r="C563" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D563">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E563" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F563" t="s">
+        <v>315</v>
+      </c>
+      <c r="G563" t="str">
+        <f>VLOOKUP(F563,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H563" t="s">
+        <v>74</v>
+      </c>
+      <c r="I563">
+        <f>VLOOKUP(H563,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>145</v>
+      </c>
+      <c r="J563" s="1">
+        <v>1</v>
+      </c>
+      <c r="K563">
+        <v>2</v>
+      </c>
+      <c r="L563" s="1">
+        <v>10</v>
+      </c>
+      <c r="M563" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="564" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A564" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B564" s="1">
+        <v>4</v>
+      </c>
+      <c r="C564" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D564">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E564" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F564" t="s">
+        <v>315</v>
+      </c>
+      <c r="G564" t="str">
+        <f>VLOOKUP(F564,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H564" t="s">
+        <v>76</v>
+      </c>
+      <c r="I564">
+        <f>VLOOKUP(H564,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>825</v>
+      </c>
+      <c r="J564" s="1">
+        <v>1</v>
+      </c>
+      <c r="L564" s="1">
+        <v>10</v>
+      </c>
+      <c r="M564" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="565" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A565" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B565" s="1">
+        <v>4</v>
+      </c>
+      <c r="C565" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D565">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E565" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F565" t="s">
+        <v>315</v>
+      </c>
+      <c r="G565" t="str">
+        <f>VLOOKUP(F565,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H565" t="s">
+        <v>110</v>
+      </c>
+      <c r="I565">
+        <f>VLOOKUP(H565,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>142</v>
+      </c>
+      <c r="J565" s="1">
+        <v>1</v>
+      </c>
+      <c r="L565" s="1">
+        <v>10</v>
+      </c>
+      <c r="M565" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="566" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A566" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B566" s="1">
+        <v>4</v>
+      </c>
+      <c r="C566" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D566">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E566" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F566" t="s">
+        <v>315</v>
+      </c>
+      <c r="G566" t="str">
+        <f>VLOOKUP(F566,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H566" t="s">
+        <v>113</v>
+      </c>
+      <c r="I566">
+        <f>VLOOKUP(H566,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>150</v>
+      </c>
+      <c r="J566" s="1">
+        <v>1</v>
+      </c>
+      <c r="K566">
+        <v>2</v>
+      </c>
+      <c r="L566" s="1">
+        <v>10</v>
+      </c>
+      <c r="M566" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="567" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A567" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B567" s="1">
+        <v>4</v>
+      </c>
+      <c r="C567" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D567">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E567" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F567" t="s">
+        <v>315</v>
+      </c>
+      <c r="G567" t="str">
+        <f>VLOOKUP(F567,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H567" t="s">
+        <v>111</v>
+      </c>
+      <c r="I567">
+        <f>VLOOKUP(H567,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>144</v>
+      </c>
+      <c r="J567" s="1">
+        <v>1</v>
+      </c>
+      <c r="K567">
+        <v>2</v>
+      </c>
+      <c r="L567" s="1">
+        <v>10</v>
+      </c>
+      <c r="M567" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A568" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B568" s="1">
+        <v>4</v>
+      </c>
+      <c r="C568" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D568">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E568" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F568" t="s">
+        <v>315</v>
+      </c>
+      <c r="G568" t="str">
+        <f>VLOOKUP(F568,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H568" t="s">
+        <v>114</v>
+      </c>
+      <c r="I568">
+        <f>VLOOKUP(H568,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>156</v>
+      </c>
+      <c r="J568" s="1">
+        <v>1</v>
+      </c>
+      <c r="K568">
+        <v>1</v>
+      </c>
+      <c r="L568" s="1">
+        <v>10</v>
+      </c>
+      <c r="M568" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A569" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B569" s="1">
+        <v>4</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D569">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E569" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F569" t="s">
+        <v>315</v>
+      </c>
+      <c r="G569" t="str">
+        <f>VLOOKUP(F569,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H569" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I569">
+        <f>VLOOKUP(H569,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>146</v>
+      </c>
+      <c r="J569" s="1">
+        <v>1</v>
+      </c>
+      <c r="K569">
+        <v>2</v>
+      </c>
+      <c r="L569" s="1">
+        <v>10</v>
+      </c>
+      <c r="M569" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="570" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A570" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B570" s="1">
+        <v>4</v>
+      </c>
+      <c r="C570" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D570">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E570" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F570" t="s">
+        <v>315</v>
+      </c>
+      <c r="G570" t="str">
+        <f>VLOOKUP(F570,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H570" t="s">
+        <v>75</v>
+      </c>
+      <c r="I570">
+        <f>VLOOKUP(H570,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>140</v>
+      </c>
+      <c r="J570" s="1">
+        <v>1</v>
+      </c>
+      <c r="L570" s="1">
+        <v>10</v>
+      </c>
+      <c r="M570" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="571" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A571" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B571" s="1">
+        <v>4</v>
+      </c>
+      <c r="C571" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D571">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E571" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F571" t="s">
+        <v>315</v>
+      </c>
+      <c r="G571" t="str">
+        <f>VLOOKUP(F571,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H571" t="s">
+        <v>269</v>
+      </c>
+      <c r="I571">
+        <f>VLOOKUP(H571,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>147</v>
+      </c>
+      <c r="J571" s="1">
+        <v>1</v>
+      </c>
+      <c r="L571" s="1">
+        <v>10</v>
+      </c>
+      <c r="M571" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="572" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A572" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B572" s="1">
+        <v>4</v>
+      </c>
+      <c r="C572" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D572">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E572" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F572" t="s">
+        <v>315</v>
+      </c>
+      <c r="G572" t="str">
+        <f>VLOOKUP(F572,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H572" t="s">
+        <v>85</v>
+      </c>
+      <c r="I572">
+        <f>VLOOKUP(H572,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>149</v>
+      </c>
+      <c r="J572" s="1">
+        <v>1</v>
+      </c>
+      <c r="L572" s="1">
+        <v>10</v>
+      </c>
+      <c r="M572" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="573" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A573" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B573" s="1">
+        <v>4</v>
+      </c>
+      <c r="C573" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D573">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E573" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F573" t="s">
+        <v>315</v>
+      </c>
+      <c r="G573" t="str">
+        <f>VLOOKUP(F573,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H573" t="s">
+        <v>86</v>
+      </c>
+      <c r="I573">
+        <f>VLOOKUP(H573,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>148</v>
+      </c>
+      <c r="J573" s="1">
+        <v>1</v>
+      </c>
+      <c r="L573" s="1">
+        <v>10</v>
+      </c>
+      <c r="M573" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="574" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A574" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B574" s="1">
+        <v>4</v>
+      </c>
+      <c r="C574" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D574">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E574" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F574" t="s">
+        <v>315</v>
+      </c>
+      <c r="G574" t="str">
+        <f>VLOOKUP(F574,Sayfa2!A:B,2,0)</f>
+        <v>a8af8331-0c65-49e1-94aa-e2abac635749</v>
+      </c>
+      <c r="H574" t="s">
+        <v>322</v>
+      </c>
+      <c r="I574">
+        <f>VLOOKUP(H574,Sayfa2!$H$81:$I$105,2,0)</f>
+        <v>151</v>
+      </c>
+      <c r="J574" s="1">
+        <v>1</v>
+      </c>
+      <c r="L574" s="1">
+        <v>10</v>
+      </c>
+      <c r="M574" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="575" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A575" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B575" s="1">
+        <v>4</v>
+      </c>
+      <c r="C575" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D575">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E575" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F575" t="s">
+        <v>314</v>
+      </c>
+      <c r="G575" t="str">
+        <f>VLOOKUP(F575,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H575" t="s">
+        <v>18</v>
+      </c>
+      <c r="I575">
+        <f>VLOOKUP(H575,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>109</v>
+      </c>
+      <c r="J575" s="1">
+        <v>1</v>
+      </c>
+      <c r="K575">
+        <v>4</v>
+      </c>
+      <c r="L575" s="1">
+        <v>10</v>
+      </c>
+      <c r="M575" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="576" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A576" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B576" s="1">
+        <v>4</v>
+      </c>
+      <c r="C576" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D576">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E576" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F576" t="s">
+        <v>314</v>
+      </c>
+      <c r="G576" t="str">
+        <f>VLOOKUP(F576,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H576" t="s">
+        <v>265</v>
+      </c>
+      <c r="I576">
+        <f>VLOOKUP(H576,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>124</v>
+      </c>
+      <c r="J576" s="1">
+        <v>1</v>
+      </c>
+      <c r="K576">
+        <v>4</v>
+      </c>
+      <c r="L576" s="1">
+        <v>10</v>
+      </c>
+      <c r="M576" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="577" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A577" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B577" s="1">
+        <v>4</v>
+      </c>
+      <c r="C577" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D577">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="E577" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F577" t="s">
+        <v>314</v>
+      </c>
+      <c r="G577" t="str">
+        <f>VLOOKUP(F577,Sayfa2!A:B,2,0)</f>
+        <v>38ba7340-72b8-434b-a246-def36b7db42a</v>
+      </c>
+      <c r="H577" t="s">
+        <v>78</v>
+      </c>
+      <c r="I577">
+        <f>VLOOKUP(H577,Sayfa2!$H$49:$I$80,2,0)</f>
+        <v>13</v>
+      </c>
+      <c r="J577" s="1">
+        <v>1</v>
+      </c>
+      <c r="K577">
+        <v>4</v>
+      </c>
+      <c r="L577" s="1">
+        <v>10</v>
+      </c>
+      <c r="M577" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="578" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A578" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B578" s="1">
+        <v>4</v>
+      </c>
+      <c r="C578" t="s">
+        <v>65</v>
+      </c>
+      <c r="D578">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E578" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F578" t="s">
+        <v>316</v>
+      </c>
+      <c r="G578" t="str">
+        <f>VLOOKUP(F578,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H578" t="s">
+        <v>58</v>
+      </c>
+      <c r="I578">
+        <f>VLOOKUP(H578,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>71</v>
+      </c>
+      <c r="J578" s="1">
+        <v>1</v>
+      </c>
+      <c r="K578">
+        <v>4</v>
+      </c>
+      <c r="L578" s="1">
+        <v>10</v>
+      </c>
+      <c r="M578" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="579" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A579" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B579" s="1">
+        <v>4</v>
+      </c>
+      <c r="C579" t="s">
+        <v>65</v>
+      </c>
+      <c r="D579">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E579" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F579" t="s">
+        <v>316</v>
+      </c>
+      <c r="G579" t="str">
+        <f>VLOOKUP(F579,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H579" t="s">
+        <v>66</v>
+      </c>
+      <c r="I579">
+        <f>VLOOKUP(H579,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="J579" s="1">
+        <v>1</v>
+      </c>
+      <c r="K579">
+        <v>8</v>
+      </c>
+      <c r="L579" s="1">
+        <v>10</v>
+      </c>
+      <c r="M579" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="580" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A580" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B580" s="1">
+        <v>4</v>
+      </c>
+      <c r="C580" t="s">
+        <v>65</v>
+      </c>
+      <c r="D580">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E580" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F580" t="s">
+        <v>316</v>
+      </c>
+      <c r="G580" t="str">
+        <f>VLOOKUP(F580,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H580" t="s">
+        <v>67</v>
+      </c>
+      <c r="I580">
+        <f>VLOOKUP(H580,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>70</v>
+      </c>
+      <c r="J580" s="1">
+        <v>1</v>
+      </c>
+      <c r="K580">
+        <v>5</v>
+      </c>
+      <c r="L580" s="1">
+        <v>10</v>
+      </c>
+      <c r="M580" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="581" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A581" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B581" s="1">
+        <v>4</v>
+      </c>
+      <c r="C581" t="s">
+        <v>65</v>
+      </c>
+      <c r="D581">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E581" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F581" t="s">
+        <v>316</v>
+      </c>
+      <c r="G581" t="str">
+        <f>VLOOKUP(F581,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H581" t="s">
+        <v>68</v>
+      </c>
+      <c r="I581">
+        <f>VLOOKUP(H581,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="J581" s="1">
+        <v>1</v>
+      </c>
+      <c r="K581">
+        <v>4</v>
+      </c>
+      <c r="L581" s="1">
+        <v>10</v>
+      </c>
+      <c r="M581" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="582" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A582" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B582" s="1">
+        <v>4</v>
+      </c>
+      <c r="C582" t="s">
+        <v>65</v>
+      </c>
+      <c r="D582">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E582" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F582" t="s">
+        <v>316</v>
+      </c>
+      <c r="G582" t="str">
+        <f>VLOOKUP(F582,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H582" t="s">
+        <v>60</v>
+      </c>
+      <c r="I582">
+        <f>VLOOKUP(H582,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>77</v>
+      </c>
+      <c r="J582" s="1">
+        <v>1</v>
+      </c>
+      <c r="K582">
+        <v>12</v>
+      </c>
+      <c r="L582" s="1">
+        <v>10</v>
+      </c>
+      <c r="M582" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="583" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A583" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B583" s="1">
+        <v>4</v>
+      </c>
+      <c r="C583" t="s">
+        <v>65</v>
+      </c>
+      <c r="D583">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E583" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F583" t="s">
+        <v>316</v>
+      </c>
+      <c r="G583" t="str">
+        <f>VLOOKUP(F583,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H583" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I583">
+        <f>VLOOKUP(H583,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>100</v>
+      </c>
+      <c r="J583" s="1">
+        <v>1</v>
+      </c>
+      <c r="K583">
+        <v>2</v>
+      </c>
+      <c r="L583" s="1">
+        <v>10</v>
+      </c>
+      <c r="M583" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="584" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A584" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B584" s="1">
+        <v>4</v>
+      </c>
+      <c r="C584" t="s">
+        <v>65</v>
+      </c>
+      <c r="D584">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E584" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F584" t="s">
+        <v>316</v>
+      </c>
+      <c r="G584" t="str">
+        <f>VLOOKUP(F584,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H584" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="I584">
+        <f>VLOOKUP(H584,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>91</v>
+      </c>
+      <c r="J584" s="1">
+        <v>1</v>
+      </c>
+      <c r="K584">
+        <v>4</v>
+      </c>
+      <c r="L584" s="1">
+        <v>10</v>
+      </c>
+      <c r="M584" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="585" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A585" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B585" s="1">
+        <v>4</v>
+      </c>
+      <c r="C585" t="s">
+        <v>65</v>
+      </c>
+      <c r="D585">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E585" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F585" t="s">
+        <v>316</v>
+      </c>
+      <c r="G585" t="str">
+        <f>VLOOKUP(F585,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H585" t="s">
+        <v>61</v>
+      </c>
+      <c r="I585">
+        <f>VLOOKUP(H585,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>79</v>
+      </c>
+      <c r="J585" s="1">
+        <v>1</v>
+      </c>
+      <c r="L585" s="1">
+        <v>10</v>
+      </c>
+      <c r="M585" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="586" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A586" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B586" s="1">
+        <v>4</v>
+      </c>
+      <c r="C586" t="s">
+        <v>65</v>
+      </c>
+      <c r="D586">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E586" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F586" t="s">
+        <v>316</v>
+      </c>
+      <c r="G586" t="str">
+        <f>VLOOKUP(F586,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H586" t="s">
+        <v>69</v>
+      </c>
+      <c r="I586">
+        <f>VLOOKUP(H586,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>101</v>
+      </c>
+      <c r="J586" s="1">
+        <v>1</v>
+      </c>
+      <c r="K586">
+        <v>2</v>
+      </c>
+      <c r="L586" s="1">
+        <v>10</v>
+      </c>
+      <c r="M586" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="587" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A587" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B587" s="1">
+        <v>4</v>
+      </c>
+      <c r="C587" t="s">
+        <v>65</v>
+      </c>
+      <c r="D587">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E587" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F587" t="s">
+        <v>316</v>
+      </c>
+      <c r="G587" t="str">
+        <f>VLOOKUP(F587,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H587" t="s">
+        <v>70</v>
+      </c>
+      <c r="I587">
+        <f>VLOOKUP(H587,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>80</v>
+      </c>
+      <c r="J587" s="1">
+        <v>1</v>
+      </c>
+      <c r="L587" s="1">
+        <v>10</v>
+      </c>
+      <c r="M587" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="588" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A588" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B588" s="1">
+        <v>4</v>
+      </c>
+      <c r="C588" t="s">
+        <v>65</v>
+      </c>
+      <c r="D588">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E588" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F588" t="s">
+        <v>316</v>
+      </c>
+      <c r="G588" t="str">
+        <f>VLOOKUP(F588,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H588" t="s">
+        <v>274</v>
+      </c>
+      <c r="I588">
+        <f>VLOOKUP(H588,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>789</v>
+      </c>
+      <c r="J588" s="1">
+        <v>1</v>
+      </c>
+      <c r="L588" s="1">
+        <v>10</v>
+      </c>
+      <c r="M588" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="589" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A589" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B589" s="1">
+        <v>4</v>
+      </c>
+      <c r="C589" t="s">
+        <v>65</v>
+      </c>
+      <c r="D589">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E589" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F589" t="s">
+        <v>316</v>
+      </c>
+      <c r="G589" t="str">
+        <f>VLOOKUP(F589,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H589" t="s">
+        <v>276</v>
+      </c>
+      <c r="I589">
+        <f>VLOOKUP(H589,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>790</v>
+      </c>
+      <c r="J589" s="1">
+        <v>1</v>
+      </c>
+      <c r="L589" s="1">
+        <v>10</v>
+      </c>
+      <c r="M589" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="590" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A590" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B590" s="1">
+        <v>4</v>
+      </c>
+      <c r="C590" t="s">
+        <v>65</v>
+      </c>
+      <c r="D590">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E590" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F590" t="s">
+        <v>316</v>
+      </c>
+      <c r="G590" t="str">
+        <f>VLOOKUP(F590,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H590" t="s">
+        <v>71</v>
+      </c>
+      <c r="I590">
+        <f>VLOOKUP(H590,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>792</v>
+      </c>
+      <c r="J590" s="1">
+        <v>1</v>
+      </c>
+      <c r="L590" s="1">
+        <v>10</v>
+      </c>
+      <c r="M590" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="591" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A591" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B591" s="1">
+        <v>4</v>
+      </c>
+      <c r="C591" t="s">
+        <v>65</v>
+      </c>
+      <c r="D591">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E591" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F591" t="s">
+        <v>316</v>
+      </c>
+      <c r="G591" t="str">
+        <f>VLOOKUP(F591,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H591" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="I591">
+        <f>VLOOKUP(H591,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>791</v>
+      </c>
+      <c r="J591" s="1">
+        <v>1</v>
+      </c>
+      <c r="L591" s="1">
+        <v>10</v>
+      </c>
+      <c r="M591" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="592" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A592" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B592" s="1">
+        <v>4</v>
+      </c>
+      <c r="C592" t="s">
+        <v>65</v>
+      </c>
+      <c r="D592">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E592" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F592" t="s">
+        <v>318</v>
+      </c>
+      <c r="G592" t="str">
+        <f>VLOOKUP(F592,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H592" t="s">
+        <v>16</v>
+      </c>
+      <c r="I592">
+        <f>VLOOKUP(H592,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="J592" s="1">
+        <v>1</v>
+      </c>
+      <c r="K592">
+        <v>21</v>
+      </c>
+      <c r="L592" s="1">
+        <v>10</v>
+      </c>
+      <c r="M592" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="593" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A593" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B593" s="1">
+        <v>4</v>
+      </c>
+      <c r="C593" t="s">
+        <v>65</v>
+      </c>
+      <c r="D593">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E593" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F593" t="s">
+        <v>318</v>
+      </c>
+      <c r="G593" t="str">
+        <f>VLOOKUP(F593,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H593" t="s">
+        <v>28</v>
+      </c>
+      <c r="I593">
+        <f>VLOOKUP(H593,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>1</v>
+      </c>
+      <c r="J593" s="1">
+        <v>1</v>
+      </c>
+      <c r="K593">
+        <v>9</v>
+      </c>
+      <c r="L593" s="1">
+        <v>10</v>
+      </c>
+      <c r="M593" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="594" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A594" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B594" s="1">
+        <v>4</v>
+      </c>
+      <c r="C594" t="s">
+        <v>65</v>
+      </c>
+      <c r="D594">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E594" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F594" t="s">
+        <v>318</v>
+      </c>
+      <c r="G594" t="str">
+        <f>VLOOKUP(F594,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H594" t="s">
+        <v>31</v>
+      </c>
+      <c r="I594">
+        <f>VLOOKUP(H594,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>30</v>
+      </c>
+      <c r="J594" s="1">
+        <v>1</v>
+      </c>
+      <c r="K594">
+        <v>6</v>
+      </c>
+      <c r="L594" s="1">
+        <v>10</v>
+      </c>
+      <c r="M594" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="595" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A595" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B595" s="1">
+        <v>4</v>
+      </c>
+      <c r="C595" t="s">
+        <v>65</v>
+      </c>
+      <c r="D595">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E595" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F595" t="s">
+        <v>318</v>
+      </c>
+      <c r="G595" t="str">
+        <f>VLOOKUP(F595,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H595" t="s">
+        <v>45</v>
+      </c>
+      <c r="I595">
+        <f>VLOOKUP(H595,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>33</v>
+      </c>
+      <c r="J595" s="1">
+        <v>1</v>
+      </c>
+      <c r="K595">
+        <v>6</v>
+      </c>
+      <c r="L595" s="1">
+        <v>10</v>
+      </c>
+      <c r="M595" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="596" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A596" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B596" s="1">
+        <v>4</v>
+      </c>
+      <c r="C596" t="s">
+        <v>65</v>
+      </c>
+      <c r="D596">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E596" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F596" t="s">
+        <v>318</v>
+      </c>
+      <c r="G596" t="str">
+        <f>VLOOKUP(F596,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H596" t="s">
+        <v>46</v>
+      </c>
+      <c r="I596">
+        <f>VLOOKUP(H596,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>57</v>
+      </c>
+      <c r="J596" s="1">
+        <v>1</v>
+      </c>
+      <c r="K596">
+        <v>2</v>
+      </c>
+      <c r="L596" s="1">
+        <v>10</v>
+      </c>
+      <c r="M596" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="597" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A597" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B597" s="1">
+        <v>4</v>
+      </c>
+      <c r="C597" t="s">
+        <v>65</v>
+      </c>
+      <c r="D597">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E597" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F597" t="s">
+        <v>319</v>
+      </c>
+      <c r="G597" t="str">
+        <f>VLOOKUP(F597,Sayfa2!A:B,2,0)</f>
+        <v>e8b38ebc-0c41-4bdf-b228-f3ba7d136dd0</v>
+      </c>
+      <c r="H597" t="s">
+        <v>63</v>
+      </c>
+      <c r="I597">
+        <f>VLOOKUP(H597,Sayfa2!$H$173:$I$180,2,0)</f>
+        <v>6</v>
+      </c>
+      <c r="J597" s="1">
+        <v>1</v>
+      </c>
+      <c r="L597" s="1">
+        <v>10</v>
+      </c>
+      <c r="M597" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="598" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A598" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B598" s="1">
+        <v>4</v>
+      </c>
+      <c r="C598" t="s">
+        <v>65</v>
+      </c>
+      <c r="D598">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E598" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F598" t="s">
+        <v>319</v>
+      </c>
+      <c r="G598" t="str">
+        <f>VLOOKUP(F598,Sayfa2!A:B,2,0)</f>
+        <v>e8b38ebc-0c41-4bdf-b228-f3ba7d136dd0</v>
+      </c>
+      <c r="H598" t="s">
+        <v>64</v>
+      </c>
+      <c r="I598">
+        <f>VLOOKUP(H598,Sayfa2!$H$173:$I$180,2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="J598" s="1">
+        <v>1</v>
+      </c>
+      <c r="K598">
+        <v>16</v>
+      </c>
+      <c r="L598" s="1">
+        <v>10</v>
+      </c>
+      <c r="M598" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="599" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A599" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B599" s="1">
+        <v>4</v>
+      </c>
+      <c r="C599" t="s">
+        <v>65</v>
+      </c>
+      <c r="D599">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E599" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F599" t="s">
+        <v>319</v>
+      </c>
+      <c r="G599" t="str">
+        <f>VLOOKUP(F599,Sayfa2!A:B,2,0)</f>
+        <v>e8b38ebc-0c41-4bdf-b228-f3ba7d136dd0</v>
+      </c>
+      <c r="H599" t="s">
+        <v>143</v>
+      </c>
+      <c r="I599">
+        <f>VLOOKUP(H599,Sayfa2!$H$173:$I$180,2,0)</f>
+        <v>15</v>
+      </c>
+      <c r="J599" s="1">
+        <v>1</v>
+      </c>
+      <c r="K599">
+        <v>4</v>
+      </c>
+      <c r="L599" s="1">
+        <v>10</v>
+      </c>
+      <c r="M599" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="600" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A600" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B600" s="1">
+        <v>4</v>
+      </c>
+      <c r="C600" t="s">
+        <v>65</v>
+      </c>
+      <c r="D600">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E600" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F600" t="s">
+        <v>319</v>
+      </c>
+      <c r="G600" t="str">
+        <f>VLOOKUP(F600,Sayfa2!A:B,2,0)</f>
+        <v>e8b38ebc-0c41-4bdf-b228-f3ba7d136dd0</v>
+      </c>
+      <c r="H600" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I600">
+        <f>VLOOKUP(H600,Sayfa2!$H$173:$I$180,2,0)</f>
+        <v>17</v>
+      </c>
+      <c r="J600" s="1">
+        <v>1</v>
+      </c>
+      <c r="K600">
+        <v>12</v>
+      </c>
+      <c r="L600" s="1">
+        <v>10</v>
+      </c>
+      <c r="M600" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="601" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A601" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B601" s="1">
+        <v>4</v>
+      </c>
+      <c r="C601" t="s">
+        <v>65</v>
+      </c>
+      <c r="D601">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E601" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F601" t="s">
+        <v>319</v>
+      </c>
+      <c r="G601" t="str">
+        <f>VLOOKUP(F601,Sayfa2!A:B,2,0)</f>
+        <v>e8b38ebc-0c41-4bdf-b228-f3ba7d136dd0</v>
+      </c>
+      <c r="H601" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I601">
+        <f>VLOOKUP(H601,Sayfa2!$H$173:$I$180,2,0)</f>
+        <v>18</v>
+      </c>
+      <c r="J601" s="1">
+        <v>1</v>
+      </c>
+      <c r="K601">
+        <v>12</v>
+      </c>
+      <c r="L601" s="1">
+        <v>10</v>
+      </c>
+      <c r="M601" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="602" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A602" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B602" s="1">
+        <v>4</v>
+      </c>
+      <c r="C602" t="s">
+        <v>65</v>
+      </c>
+      <c r="D602">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="E602" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F602" t="s">
+        <v>319</v>
+      </c>
+      <c r="G602" t="str">
+        <f>VLOOKUP(F602,Sayfa2!A:B,2,0)</f>
+        <v>e8b38ebc-0c41-4bdf-b228-f3ba7d136dd0</v>
+      </c>
+      <c r="H602" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I602">
+        <f>VLOOKUP(H602,Sayfa2!$H$173:$I$180,2,0)</f>
+        <v>793</v>
+      </c>
+      <c r="J602" s="1">
+        <v>1</v>
+      </c>
+      <c r="L602" s="1">
+        <v>10</v>
+      </c>
+      <c r="M602" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="603" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A603" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B603" s="1">
+        <v>4</v>
+      </c>
+      <c r="C603" t="s">
+        <v>43</v>
+      </c>
+      <c r="D603">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E603" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F603" t="s">
+        <v>130</v>
+      </c>
+      <c r="G603" t="str">
+        <f>VLOOKUP(F603,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H603" t="s">
+        <v>33</v>
+      </c>
+      <c r="I603">
+        <f>VLOOKUP(H603,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>20</v>
+      </c>
+      <c r="J603" s="1">
+        <v>1</v>
+      </c>
+      <c r="K603">
+        <v>3</v>
+      </c>
+      <c r="L603" s="1">
+        <v>10</v>
+      </c>
+      <c r="M603" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="604" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A604" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B604" s="1">
+        <v>4</v>
+      </c>
+      <c r="C604" t="s">
+        <v>43</v>
+      </c>
+      <c r="D604">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E604" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F604" t="s">
+        <v>130</v>
+      </c>
+      <c r="G604" t="str">
+        <f>VLOOKUP(F604,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H604" t="s">
+        <v>34</v>
+      </c>
+      <c r="I604">
+        <f>VLOOKUP(H604,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>21</v>
+      </c>
+      <c r="J604" s="1">
+        <v>1</v>
+      </c>
+      <c r="K604">
+        <v>6</v>
+      </c>
+      <c r="L604" s="1">
+        <v>10</v>
+      </c>
+      <c r="M604" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="605" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A605" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B605" s="1">
+        <v>4</v>
+      </c>
+      <c r="C605" t="s">
+        <v>43</v>
+      </c>
+      <c r="D605">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E605" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F605" t="s">
+        <v>130</v>
+      </c>
+      <c r="G605" t="str">
+        <f>VLOOKUP(F605,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H605" t="s">
+        <v>35</v>
+      </c>
+      <c r="I605">
+        <f>VLOOKUP(H605,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>24</v>
+      </c>
+      <c r="J605" s="1">
+        <v>1</v>
+      </c>
+      <c r="K605">
+        <v>3</v>
+      </c>
+      <c r="L605" s="1">
+        <v>10</v>
+      </c>
+      <c r="M605" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="606" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A606" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B606" s="1">
+        <v>4</v>
+      </c>
+      <c r="C606" t="s">
+        <v>43</v>
+      </c>
+      <c r="D606">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E606" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F606" t="s">
+        <v>130</v>
+      </c>
+      <c r="G606" t="str">
+        <f>VLOOKUP(F606,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H606" t="s">
+        <v>47</v>
+      </c>
+      <c r="I606">
+        <f>VLOOKUP(H606,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>802</v>
+      </c>
+      <c r="J606" s="1">
+        <v>1</v>
+      </c>
+      <c r="K606">
+        <v>3</v>
+      </c>
+      <c r="L606" s="1">
+        <v>10</v>
+      </c>
+      <c r="M606" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="607" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A607" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B607" s="1">
+        <v>4</v>
+      </c>
+      <c r="C607" t="s">
+        <v>43</v>
+      </c>
+      <c r="D607">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E607" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F607" t="s">
+        <v>318</v>
+      </c>
+      <c r="G607" t="str">
+        <f>VLOOKUP(F607,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H607" t="s">
+        <v>16</v>
+      </c>
+      <c r="I607">
+        <f>VLOOKUP(H607,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="J607" s="1">
+        <v>1</v>
+      </c>
+      <c r="K607">
+        <v>7</v>
+      </c>
+      <c r="L607" s="1">
+        <v>10</v>
+      </c>
+      <c r="M607" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="608" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A608" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B608" s="1">
+        <v>4</v>
+      </c>
+      <c r="C608" t="s">
+        <v>43</v>
+      </c>
+      <c r="D608">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E608" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F608" t="s">
+        <v>318</v>
+      </c>
+      <c r="G608" t="str">
+        <f>VLOOKUP(F608,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H608" t="s">
+        <v>28</v>
+      </c>
+      <c r="I608">
+        <f>VLOOKUP(H608,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>1</v>
+      </c>
+      <c r="J608" s="1">
+        <v>1</v>
+      </c>
+      <c r="K608">
+        <v>2</v>
+      </c>
+      <c r="L608" s="1">
+        <v>10</v>
+      </c>
+      <c r="M608" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="609" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A609" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B609" s="1">
+        <v>4</v>
+      </c>
+      <c r="C609" t="s">
+        <v>43</v>
+      </c>
+      <c r="D609">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E609" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F609" t="s">
+        <v>318</v>
+      </c>
+      <c r="G609" t="str">
+        <f>VLOOKUP(F609,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H609" t="s">
+        <v>31</v>
+      </c>
+      <c r="I609">
+        <f>VLOOKUP(H609,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>30</v>
+      </c>
+      <c r="J609" s="1">
+        <v>1</v>
+      </c>
+      <c r="K609">
+        <v>2</v>
+      </c>
+      <c r="L609" s="1">
+        <v>10</v>
+      </c>
+      <c r="M609" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="610" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A610" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B610" s="1">
+        <v>4</v>
+      </c>
+      <c r="C610" t="s">
+        <v>43</v>
+      </c>
+      <c r="D610">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E610" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F610" t="s">
+        <v>318</v>
+      </c>
+      <c r="G610" t="str">
+        <f>VLOOKUP(F610,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H610" t="s">
+        <v>45</v>
+      </c>
+      <c r="I610">
+        <f>VLOOKUP(H610,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>33</v>
+      </c>
+      <c r="J610" s="1">
+        <v>1</v>
+      </c>
+      <c r="K610">
+        <v>2</v>
+      </c>
+      <c r="L610" s="1">
+        <v>10</v>
+      </c>
+      <c r="M610" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="611" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A611" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B611" s="1">
+        <v>4</v>
+      </c>
+      <c r="C611" t="s">
+        <v>43</v>
+      </c>
+      <c r="D611">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E611" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F611" t="s">
+        <v>318</v>
+      </c>
+      <c r="G611" t="str">
+        <f>VLOOKUP(F611,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H611" t="s">
+        <v>56</v>
+      </c>
+      <c r="I611">
+        <f>VLOOKUP(H611,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>32</v>
+      </c>
+      <c r="J611" s="1">
+        <v>1</v>
+      </c>
+      <c r="L611" s="1">
+        <v>10</v>
+      </c>
+      <c r="M611" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="612" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A612" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B612" s="1">
+        <v>4</v>
+      </c>
+      <c r="C612" t="s">
+        <v>43</v>
+      </c>
+      <c r="D612">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E612" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F612" t="s">
+        <v>318</v>
+      </c>
+      <c r="G612" t="str">
+        <f>VLOOKUP(F612,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H612" t="s">
+        <v>46</v>
+      </c>
+      <c r="I612">
+        <f>VLOOKUP(H612,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>57</v>
+      </c>
+      <c r="J612" s="1">
+        <v>1</v>
+      </c>
+      <c r="K612">
+        <v>2</v>
+      </c>
+      <c r="L612" s="1">
+        <v>10</v>
+      </c>
+      <c r="M612" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="613" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A613" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B613" s="1">
+        <v>4</v>
+      </c>
+      <c r="C613" t="s">
+        <v>43</v>
+      </c>
+      <c r="D613">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E613" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F613" t="s">
+        <v>39</v>
+      </c>
+      <c r="G613" t="str">
+        <f>VLOOKUP(F613,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H613" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I613">
+        <f>VLOOKUP(H613,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>81</v>
+      </c>
+      <c r="J613" s="1">
+        <v>1</v>
+      </c>
+      <c r="K613">
+        <v>7</v>
+      </c>
+      <c r="L613" s="1">
+        <v>10</v>
+      </c>
+      <c r="M613" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="614" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A614" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B614" s="1">
+        <v>4</v>
+      </c>
+      <c r="C614" t="s">
+        <v>43</v>
+      </c>
+      <c r="D614">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="E614" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F614" t="s">
+        <v>39</v>
+      </c>
+      <c r="G614" t="str">
+        <f>VLOOKUP(F614,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H614" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I614">
+        <f>VLOOKUP(H614,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>86</v>
+      </c>
+      <c r="J614" s="1">
+        <v>1</v>
+      </c>
+      <c r="K614">
+        <v>6</v>
+      </c>
+      <c r="L614" s="1">
+        <v>10</v>
+      </c>
+      <c r="M614" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="615" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A615" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B615" s="1">
+        <v>4</v>
+      </c>
+      <c r="C615" t="s">
+        <v>43</v>
+      </c>
+      <c r="D615">
+        <f t="shared" ref="D615:D632" si="4">VLOOKUP(C615,$C$2:$D$352,2,0)</f>
+        <v>43</v>
+      </c>
+      <c r="E615" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F615" t="s">
+        <v>39</v>
+      </c>
+      <c r="G615" t="str">
+        <f>VLOOKUP(F615,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H615" t="s">
+        <v>42</v>
+      </c>
+      <c r="I615">
+        <f>VLOOKUP(H615,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>87</v>
+      </c>
+      <c r="J615" s="1">
+        <v>1</v>
+      </c>
+      <c r="K615">
+        <v>2</v>
+      </c>
+      <c r="L615" s="1">
+        <v>10</v>
+      </c>
+      <c r="M615" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="616" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A616" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B616" s="1">
+        <v>4</v>
+      </c>
+      <c r="C616" t="s">
+        <v>43</v>
+      </c>
+      <c r="D616">
+        <f t="shared" si="4"/>
+        <v>43</v>
+      </c>
+      <c r="E616" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F616" t="s">
+        <v>39</v>
+      </c>
+      <c r="G616" t="str">
+        <f>VLOOKUP(F616,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H616" t="s">
+        <v>44</v>
+      </c>
+      <c r="I616">
+        <f>VLOOKUP(H616,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>82</v>
+      </c>
+      <c r="J616" s="1">
+        <v>1</v>
+      </c>
+      <c r="L616" s="1">
+        <v>10</v>
+      </c>
+      <c r="M616" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="617" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A617" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B617" s="1">
+        <v>4</v>
+      </c>
+      <c r="C617" t="s">
+        <v>32</v>
+      </c>
+      <c r="D617">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E617" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F617" t="s">
+        <v>130</v>
+      </c>
+      <c r="G617" t="str">
+        <f>VLOOKUP(F617,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H617" t="s">
+        <v>33</v>
+      </c>
+      <c r="I617">
+        <f>VLOOKUP(H617,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>20</v>
+      </c>
+      <c r="J617" s="1">
+        <v>1</v>
+      </c>
+      <c r="K617">
+        <v>2</v>
+      </c>
+      <c r="L617" s="1">
+        <v>10</v>
+      </c>
+      <c r="M617" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="618" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A618" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B618" s="1">
+        <v>4</v>
+      </c>
+      <c r="C618" t="s">
+        <v>32</v>
+      </c>
+      <c r="D618">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E618" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F618" t="s">
+        <v>130</v>
+      </c>
+      <c r="G618" t="str">
+        <f>VLOOKUP(F618,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H618" t="s">
+        <v>34</v>
+      </c>
+      <c r="I618">
+        <f>VLOOKUP(H618,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>21</v>
+      </c>
+      <c r="J618" s="1">
+        <v>1</v>
+      </c>
+      <c r="K618">
+        <v>5</v>
+      </c>
+      <c r="L618" s="1">
+        <v>10</v>
+      </c>
+      <c r="M618" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="619" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A619" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B619" s="1">
+        <v>4</v>
+      </c>
+      <c r="C619" t="s">
+        <v>32</v>
+      </c>
+      <c r="D619">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E619" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F619" t="s">
+        <v>130</v>
+      </c>
+      <c r="G619" t="str">
+        <f>VLOOKUP(F619,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H619" t="s">
+        <v>35</v>
+      </c>
+      <c r="I619">
+        <f>VLOOKUP(H619,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>24</v>
+      </c>
+      <c r="J619" s="1">
+        <v>1</v>
+      </c>
+      <c r="K619">
+        <v>5</v>
+      </c>
+      <c r="L619" s="1">
+        <v>10</v>
+      </c>
+      <c r="M619" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="620" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A620" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B620" s="1">
+        <v>4</v>
+      </c>
+      <c r="C620" t="s">
+        <v>32</v>
+      </c>
+      <c r="D620">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E620" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F620" t="s">
+        <v>130</v>
+      </c>
+      <c r="G620" t="str">
+        <f>VLOOKUP(F620,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H620" t="s">
+        <v>36</v>
+      </c>
+      <c r="I620">
+        <f>VLOOKUP(H620,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>799</v>
+      </c>
+      <c r="J620" s="1">
+        <v>1</v>
+      </c>
+      <c r="K620">
+        <v>3</v>
+      </c>
+      <c r="L620" s="1">
+        <v>10</v>
+      </c>
+      <c r="M620" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="621" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A621" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B621" s="1">
+        <v>4</v>
+      </c>
+      <c r="C621" t="s">
+        <v>32</v>
+      </c>
+      <c r="D621">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E621" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F621" t="s">
+        <v>130</v>
+      </c>
+      <c r="G621" t="str">
+        <f>VLOOKUP(F621,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H621" t="s">
+        <v>37</v>
+      </c>
+      <c r="I621">
+        <f>VLOOKUP(H621,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>800</v>
+      </c>
+      <c r="J621" s="1">
+        <v>1</v>
+      </c>
+      <c r="K621">
+        <v>1</v>
+      </c>
+      <c r="L621" s="1">
+        <v>10</v>
+      </c>
+      <c r="M621" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="622" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A622" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B622" s="1">
+        <v>4</v>
+      </c>
+      <c r="C622" t="s">
+        <v>32</v>
+      </c>
+      <c r="D622">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E622" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F622" t="s">
+        <v>317</v>
+      </c>
+      <c r="G622" t="str">
+        <f>VLOOKUP(F622,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H622" t="s">
+        <v>26</v>
+      </c>
+      <c r="I622">
+        <f>VLOOKUP(H622,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>27</v>
+      </c>
+      <c r="J622" s="1">
+        <v>1</v>
+      </c>
+      <c r="K622">
+        <v>2</v>
+      </c>
+      <c r="L622" s="1">
+        <v>10</v>
+      </c>
+      <c r="M622" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="623" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A623" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B623" s="1">
+        <v>4</v>
+      </c>
+      <c r="C623" t="s">
+        <v>32</v>
+      </c>
+      <c r="D623">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E623" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F623" t="s">
+        <v>317</v>
+      </c>
+      <c r="G623" t="str">
+        <f>VLOOKUP(F623,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H623" t="s">
+        <v>25</v>
+      </c>
+      <c r="I623">
+        <f>VLOOKUP(H623,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>26</v>
+      </c>
+      <c r="J623" s="1">
+        <v>1</v>
+      </c>
+      <c r="K623">
+        <v>2</v>
+      </c>
+      <c r="L623" s="1">
+        <v>10</v>
+      </c>
+      <c r="M623" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="624" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A624" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B624" s="1">
+        <v>4</v>
+      </c>
+      <c r="C624" t="s">
+        <v>32</v>
+      </c>
+      <c r="D624">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E624" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F624" t="s">
+        <v>317</v>
+      </c>
+      <c r="G624" t="str">
+        <f>VLOOKUP(F624,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H624" t="s">
+        <v>120</v>
+      </c>
+      <c r="I624">
+        <f>VLOOKUP(H624,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>11</v>
+      </c>
+      <c r="J624" s="1">
+        <v>1</v>
+      </c>
+      <c r="K624">
+        <v>2</v>
+      </c>
+      <c r="L624" s="1">
+        <v>10</v>
+      </c>
+      <c r="M624" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="625" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A625" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B625" s="1">
+        <v>4</v>
+      </c>
+      <c r="C625" t="s">
+        <v>32</v>
+      </c>
+      <c r="D625">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E625" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F625" t="s">
+        <v>317</v>
+      </c>
+      <c r="G625" t="str">
+        <f>VLOOKUP(F625,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H625" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I625">
+        <f>VLOOKUP(H625,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>29</v>
+      </c>
+      <c r="J625" s="1">
+        <v>1</v>
+      </c>
+      <c r="L625" s="1">
+        <v>10</v>
+      </c>
+      <c r="M625" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="626" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A626" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B626" s="1">
+        <v>4</v>
+      </c>
+      <c r="C626" t="s">
+        <v>32</v>
+      </c>
+      <c r="D626">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E626" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F626" t="s">
+        <v>317</v>
+      </c>
+      <c r="G626" t="str">
+        <f>VLOOKUP(F626,Sayfa2!A:B,2,0)</f>
+        <v>c075b044-335f-4129-a5e7-c51745591e25</v>
+      </c>
+      <c r="H626" t="s">
+        <v>38</v>
+      </c>
+      <c r="I626">
+        <f>VLOOKUP(H626,Sayfa2!$H$125:$I$131,2,0)</f>
+        <v>12</v>
+      </c>
+      <c r="J626" s="1">
+        <v>1</v>
+      </c>
+      <c r="K626">
+        <v>8</v>
+      </c>
+      <c r="L626" s="1">
+        <v>10</v>
+      </c>
+      <c r="M626" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="627" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A627" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B627" s="1">
+        <v>4</v>
+      </c>
+      <c r="C627" t="s">
+        <v>32</v>
+      </c>
+      <c r="D627">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E627" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F627" t="s">
+        <v>316</v>
+      </c>
+      <c r="G627" t="str">
+        <f>VLOOKUP(F627,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H627" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I627">
+        <f>VLOOKUP(H627,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>73</v>
+      </c>
+      <c r="J627" s="1">
+        <v>1</v>
+      </c>
+      <c r="K627">
+        <v>2</v>
+      </c>
+      <c r="L627" s="1">
+        <v>10</v>
+      </c>
+      <c r="M627" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="628" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A628" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B628" s="1">
+        <v>4</v>
+      </c>
+      <c r="C628" t="s">
+        <v>32</v>
+      </c>
+      <c r="D628">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E628" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F628" t="s">
+        <v>316</v>
+      </c>
+      <c r="G628" t="str">
+        <f>VLOOKUP(F628,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H628" t="s">
+        <v>40</v>
+      </c>
+      <c r="I628">
+        <f>VLOOKUP(H628,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>801</v>
+      </c>
+      <c r="J628" s="1">
+        <v>1</v>
+      </c>
+      <c r="K628">
+        <v>3</v>
+      </c>
+      <c r="L628" s="1">
+        <v>10</v>
+      </c>
+      <c r="M628" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="629" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A629" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B629" s="1">
+        <v>4</v>
+      </c>
+      <c r="C629" t="s">
+        <v>32</v>
+      </c>
+      <c r="D629">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E629" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F629" t="s">
+        <v>316</v>
+      </c>
+      <c r="G629" t="str">
+        <f>VLOOKUP(F629,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H629" t="s">
+        <v>44</v>
+      </c>
+      <c r="I629">
+        <f>VLOOKUP(H629,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>82</v>
+      </c>
+      <c r="J629" s="1">
+        <v>1</v>
+      </c>
+      <c r="L629" s="1">
+        <v>10</v>
+      </c>
+      <c r="M629" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="630" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A630" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B630" s="1">
+        <v>4</v>
+      </c>
+      <c r="C630" t="s">
+        <v>32</v>
+      </c>
+      <c r="D630">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E630" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F630" t="s">
+        <v>316</v>
+      </c>
+      <c r="G630" t="str">
+        <f>VLOOKUP(F630,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H630" t="s">
+        <v>41</v>
+      </c>
+      <c r="I630">
+        <f>VLOOKUP(H630,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>86</v>
+      </c>
+      <c r="J630" s="1">
+        <v>1</v>
+      </c>
+      <c r="K630">
+        <v>2</v>
+      </c>
+      <c r="L630" s="1">
+        <v>10</v>
+      </c>
+      <c r="M630" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="631" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A631" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B631" s="1">
+        <v>4</v>
+      </c>
+      <c r="C631" t="s">
+        <v>32</v>
+      </c>
+      <c r="D631">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E631" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F631" t="s">
+        <v>316</v>
+      </c>
+      <c r="G631" t="str">
+        <f>VLOOKUP(F631,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H631" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I631">
+        <f>VLOOKUP(H631,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>81</v>
+      </c>
+      <c r="J631" s="1">
+        <v>1</v>
+      </c>
+      <c r="K631">
+        <v>6</v>
+      </c>
+      <c r="L631" s="1">
+        <v>10</v>
+      </c>
+      <c r="M631" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="632" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A632" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B632" s="1">
+        <v>4</v>
+      </c>
+      <c r="C632" t="s">
+        <v>32</v>
+      </c>
+      <c r="D632">
+        <f t="shared" si="4"/>
+        <v>56</v>
+      </c>
+      <c r="E632" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F632" t="s">
+        <v>316</v>
+      </c>
+      <c r="G632" t="str">
+        <f>VLOOKUP(F632,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H632" t="s">
+        <v>42</v>
+      </c>
+      <c r="I632">
+        <f>VLOOKUP(H632,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>87</v>
+      </c>
+      <c r="J632" s="1">
+        <v>1</v>
+      </c>
+      <c r="K632">
+        <v>3</v>
+      </c>
+      <c r="L632" s="1">
+        <v>10</v>
+      </c>
+      <c r="M632" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="633" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A633" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B633" s="1">
+        <v>4</v>
+      </c>
+      <c r="C633" t="s">
+        <v>313</v>
+      </c>
+      <c r="D633">
+        <v>49</v>
+      </c>
+      <c r="E633" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F633" t="s">
+        <v>130</v>
+      </c>
+      <c r="G633" t="str">
+        <f>VLOOKUP(F633,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H633" t="s">
+        <v>12</v>
+      </c>
+      <c r="I633">
+        <f>VLOOKUP(H633,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>23</v>
+      </c>
+      <c r="J633" s="1">
+        <v>1</v>
+      </c>
+      <c r="L633" s="1">
+        <v>10</v>
+      </c>
+      <c r="M633" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="634" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A634" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B634" s="1">
+        <v>4</v>
+      </c>
+      <c r="C634" t="s">
+        <v>313</v>
+      </c>
+      <c r="D634">
+        <v>49</v>
+      </c>
+      <c r="E634" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F634" t="s">
+        <v>130</v>
+      </c>
+      <c r="G634" t="str">
+        <f>VLOOKUP(F634,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H634" t="s">
+        <v>323</v>
+      </c>
+      <c r="I634">
+        <f>VLOOKUP(H634,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>815</v>
+      </c>
+      <c r="J634" s="1">
+        <v>1</v>
+      </c>
+      <c r="K634">
+        <v>2</v>
+      </c>
+      <c r="L634" s="1">
+        <v>10</v>
+      </c>
+      <c r="M634" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="635" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A635" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B635" s="1">
+        <v>4</v>
+      </c>
+      <c r="C635" t="s">
+        <v>313</v>
+      </c>
+      <c r="D635">
+        <v>49</v>
+      </c>
+      <c r="E635" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F635" t="s">
+        <v>130</v>
+      </c>
+      <c r="G635" t="str">
+        <f>VLOOKUP(F635,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H635" t="s">
+        <v>55</v>
+      </c>
+      <c r="I635">
+        <f>VLOOKUP(H635,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>795</v>
+      </c>
+      <c r="J635" s="1">
+        <v>1</v>
+      </c>
+      <c r="K635">
+        <v>6</v>
+      </c>
+      <c r="L635" s="1">
+        <v>10</v>
+      </c>
+      <c r="M635" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="636" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A636" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B636" s="1">
+        <v>4</v>
+      </c>
+      <c r="C636" t="s">
+        <v>313</v>
+      </c>
+      <c r="D636">
+        <v>49</v>
+      </c>
+      <c r="E636" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F636" t="s">
+        <v>130</v>
+      </c>
+      <c r="G636" t="str">
+        <f>VLOOKUP(F636,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H636" t="s">
+        <v>13</v>
+      </c>
+      <c r="I636">
+        <f>VLOOKUP(H636,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>794</v>
+      </c>
+      <c r="J636" s="1">
+        <v>1</v>
+      </c>
+      <c r="K636">
+        <v>8</v>
+      </c>
+      <c r="L636" s="1">
+        <v>10</v>
+      </c>
+      <c r="M636" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="637" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A637" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B637" s="1">
+        <v>4</v>
+      </c>
+      <c r="C637" t="s">
+        <v>313</v>
+      </c>
+      <c r="D637">
+        <v>49</v>
+      </c>
+      <c r="E637" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F637" t="s">
+        <v>130</v>
+      </c>
+      <c r="G637" t="str">
+        <f>VLOOKUP(F637,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H637" t="s">
+        <v>324</v>
+      </c>
+      <c r="I637">
+        <f>VLOOKUP(H637,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>802</v>
+      </c>
+      <c r="J637" s="1">
+        <v>1</v>
+      </c>
+      <c r="K637">
+        <v>2</v>
+      </c>
+      <c r="L637" s="1">
+        <v>10</v>
+      </c>
+      <c r="M637" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="638" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A638" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B638" s="1">
+        <v>4</v>
+      </c>
+      <c r="C638" t="s">
+        <v>313</v>
+      </c>
+      <c r="D638">
+        <v>49</v>
+      </c>
+      <c r="E638" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F638" t="s">
+        <v>130</v>
+      </c>
+      <c r="G638" t="str">
+        <f>VLOOKUP(F638,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H638" t="s">
+        <v>325</v>
+      </c>
+      <c r="I638">
+        <f>VLOOKUP(H638,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>803</v>
+      </c>
+      <c r="J638" s="1">
+        <v>1</v>
+      </c>
+      <c r="K638">
+        <v>4</v>
+      </c>
+      <c r="L638" s="1">
+        <v>10</v>
+      </c>
+      <c r="M638" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="639" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A639" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B639" s="1">
+        <v>4</v>
+      </c>
+      <c r="C639" t="s">
+        <v>313</v>
+      </c>
+      <c r="D639">
+        <v>49</v>
+      </c>
+      <c r="E639" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F639" t="s">
+        <v>316</v>
+      </c>
+      <c r="G639" t="str">
+        <f>VLOOKUP(F639,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H639" t="s">
+        <v>48</v>
+      </c>
+      <c r="I639">
+        <f>VLOOKUP(H639,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>796</v>
+      </c>
+      <c r="J639" s="1">
+        <v>1</v>
+      </c>
+      <c r="L639" s="1">
+        <v>10</v>
+      </c>
+      <c r="M639" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="640" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A640" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B640" s="1">
+        <v>4</v>
+      </c>
+      <c r="C640" t="s">
+        <v>313</v>
+      </c>
+      <c r="D640">
+        <v>49</v>
+      </c>
+      <c r="E640" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F640" t="s">
+        <v>316</v>
+      </c>
+      <c r="G640" t="str">
+        <f>VLOOKUP(F640,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H640" t="s">
+        <v>230</v>
+      </c>
+      <c r="I640">
+        <f>VLOOKUP(H640,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>89</v>
+      </c>
+      <c r="J640" s="1">
+        <v>1</v>
+      </c>
+      <c r="K640">
+        <v>18</v>
+      </c>
+      <c r="L640" s="1">
+        <v>10</v>
+      </c>
+      <c r="M640" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="641" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A641" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B641" s="1">
+        <v>4</v>
+      </c>
+      <c r="C641" t="s">
+        <v>313</v>
+      </c>
+      <c r="D641">
+        <v>49</v>
+      </c>
+      <c r="E641" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F641" t="s">
+        <v>316</v>
+      </c>
+      <c r="G641" t="str">
+        <f>VLOOKUP(F641,Sayfa2!A:B,2,0)</f>
+        <v>0e41ca5e-d812-47e5-8b5b-3e018294683b</v>
+      </c>
+      <c r="H641" t="s">
+        <v>51</v>
+      </c>
+      <c r="I641">
+        <f>VLOOKUP(H641,Sayfa2!$H$2:$I$48,2,0)</f>
+        <v>75</v>
+      </c>
+      <c r="J641" s="1">
+        <v>1</v>
+      </c>
+      <c r="K641">
+        <v>4</v>
+      </c>
+      <c r="L641" s="1">
+        <v>10</v>
+      </c>
+      <c r="M641" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="642" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A642" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B642" s="1">
+        <v>4</v>
+      </c>
+      <c r="C642" t="s">
+        <v>129</v>
+      </c>
+      <c r="D642">
+        <v>51</v>
+      </c>
+      <c r="E642" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F642" t="s">
+        <v>130</v>
+      </c>
+      <c r="G642" t="str">
+        <f>VLOOKUP(F642,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H642" t="s">
+        <v>36</v>
+      </c>
+      <c r="I642">
+        <f>VLOOKUP(H642,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>799</v>
+      </c>
+      <c r="J642" s="1">
+        <v>1</v>
+      </c>
+      <c r="K642">
+        <v>4</v>
+      </c>
+      <c r="L642" s="1">
+        <v>10</v>
+      </c>
+      <c r="M642" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="643" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A643" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B643" s="1">
+        <v>4</v>
+      </c>
+      <c r="C643" t="s">
+        <v>129</v>
+      </c>
+      <c r="D643">
+        <v>51</v>
+      </c>
+      <c r="E643" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F643" t="s">
+        <v>130</v>
+      </c>
+      <c r="G643" t="str">
+        <f>VLOOKUP(F643,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H643" t="s">
+        <v>55</v>
+      </c>
+      <c r="I643">
+        <f>VLOOKUP(H643,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>795</v>
+      </c>
+      <c r="J643" s="1">
+        <v>1</v>
+      </c>
+      <c r="K643">
+        <v>7</v>
+      </c>
+      <c r="L643" s="1">
+        <v>10</v>
+      </c>
+      <c r="M643" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="644" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A644" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B644" s="1">
+        <v>4</v>
+      </c>
+      <c r="C644" t="s">
+        <v>129</v>
+      </c>
+      <c r="D644">
+        <v>51</v>
+      </c>
+      <c r="E644" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F644" t="s">
+        <v>130</v>
+      </c>
+      <c r="G644" t="str">
+        <f>VLOOKUP(F644,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H644" t="s">
+        <v>53</v>
+      </c>
+      <c r="I644">
+        <f>VLOOKUP(H644,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>794</v>
+      </c>
+      <c r="J644" s="1">
+        <v>1</v>
+      </c>
+      <c r="K644">
+        <v>15</v>
+      </c>
+      <c r="L644" s="1">
+        <v>10</v>
+      </c>
+      <c r="M644" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="645" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A645" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B645" s="1">
+        <v>4</v>
+      </c>
+      <c r="C645" t="s">
+        <v>129</v>
+      </c>
+      <c r="D645">
+        <v>51</v>
+      </c>
+      <c r="E645" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F645" t="s">
+        <v>130</v>
+      </c>
+      <c r="G645" t="str">
+        <f>VLOOKUP(F645,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H645" t="s">
+        <v>47</v>
+      </c>
+      <c r="I645">
+        <f>VLOOKUP(H645,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>802</v>
+      </c>
+      <c r="J645" s="1">
+        <v>1</v>
+      </c>
+      <c r="K645">
+        <v>3</v>
+      </c>
+      <c r="L645" s="1">
+        <v>10</v>
+      </c>
+      <c r="M645" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="646" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A646" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B646" s="1">
+        <v>4</v>
+      </c>
+      <c r="C646" t="s">
+        <v>311</v>
+      </c>
+      <c r="D646">
+        <v>151</v>
+      </c>
+      <c r="E646" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F646" t="s">
+        <v>130</v>
+      </c>
+      <c r="G646" t="str">
+        <f>VLOOKUP(F646,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H646" t="s">
+        <v>55</v>
+      </c>
+      <c r="I646">
+        <f>VLOOKUP(H646,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>795</v>
+      </c>
+      <c r="J646" s="1">
+        <v>1</v>
+      </c>
+      <c r="K646">
+        <v>2</v>
+      </c>
+      <c r="L646" s="1">
+        <v>10</v>
+      </c>
+      <c r="M646" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="647" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A647" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B647" s="1">
+        <v>4</v>
+      </c>
+      <c r="C647" t="s">
+        <v>311</v>
+      </c>
+      <c r="D647">
+        <v>151</v>
+      </c>
+      <c r="E647" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F647" t="s">
+        <v>130</v>
+      </c>
+      <c r="G647" t="str">
+        <f>VLOOKUP(F647,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H647" t="s">
+        <v>53</v>
+      </c>
+      <c r="I647">
+        <f>VLOOKUP(H647,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>794</v>
+      </c>
+      <c r="J647" s="1">
+        <v>1</v>
+      </c>
+      <c r="K647">
+        <v>6</v>
+      </c>
+      <c r="L647" s="1">
+        <v>10</v>
+      </c>
+      <c r="M647" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="648" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A648" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B648" s="1">
+        <v>4</v>
+      </c>
+      <c r="C648" t="s">
+        <v>311</v>
+      </c>
+      <c r="D648">
+        <v>151</v>
+      </c>
+      <c r="E648" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F648" t="s">
+        <v>130</v>
+      </c>
+      <c r="G648" t="str">
+        <f>VLOOKUP(F648,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H648" t="s">
+        <v>47</v>
+      </c>
+      <c r="I648">
+        <f>VLOOKUP(H648,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>802</v>
+      </c>
+      <c r="J648" s="1">
+        <v>1</v>
+      </c>
+      <c r="K648">
+        <v>4</v>
+      </c>
+      <c r="L648" s="1">
+        <v>10</v>
+      </c>
+      <c r="M648" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="649" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A649" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B649" s="1">
+        <v>4</v>
+      </c>
+      <c r="C649" t="s">
+        <v>312</v>
+      </c>
+      <c r="D649">
+        <v>55</v>
+      </c>
+      <c r="E649" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F649" t="s">
+        <v>130</v>
+      </c>
+      <c r="G649" t="str">
+        <f>VLOOKUP(F649,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H649" t="s">
+        <v>55</v>
+      </c>
+      <c r="I649">
+        <f>VLOOKUP(H649,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>795</v>
+      </c>
+      <c r="J649" s="1">
+        <v>1</v>
+      </c>
+      <c r="K649">
+        <v>3</v>
+      </c>
+      <c r="L649" s="1">
+        <v>10</v>
+      </c>
+      <c r="M649" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="650" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A650" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B650" s="1">
+        <v>4</v>
+      </c>
+      <c r="C650" t="s">
+        <v>312</v>
+      </c>
+      <c r="D650">
+        <v>55</v>
+      </c>
+      <c r="E650" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F650" t="s">
+        <v>130</v>
+      </c>
+      <c r="G650" t="str">
+        <f>VLOOKUP(F650,Sayfa2!A:B,2,0)</f>
+        <v>b37df9ef-7877-4f8a-b850-b5335cc790db</v>
+      </c>
+      <c r="H650" t="s">
+        <v>53</v>
+      </c>
+      <c r="I650">
+        <f>VLOOKUP(H650,Sayfa2!$H$106:$I$124,2,0)</f>
+        <v>794</v>
+      </c>
+      <c r="J650" s="1">
+        <v>1</v>
+      </c>
+      <c r="K650">
+        <v>6</v>
+      </c>
+      <c r="L650" s="1">
+        <v>10</v>
+      </c>
+      <c r="M650" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="651" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A651" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B651" s="1">
+        <v>4</v>
+      </c>
+      <c r="C651" t="s">
+        <v>129</v>
+      </c>
+      <c r="D651">
+        <v>51</v>
+      </c>
+      <c r="E651" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F651" t="s">
+        <v>318</v>
+      </c>
+      <c r="G651" t="str">
+        <f>VLOOKUP(F651,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H651" t="s">
+        <v>56</v>
+      </c>
+      <c r="I651">
+        <f>VLOOKUP(H651,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>32</v>
+      </c>
+      <c r="J651" s="1">
+        <v>1</v>
+      </c>
+      <c r="K651">
+        <v>2</v>
+      </c>
+      <c r="L651" s="1">
+        <v>10</v>
+      </c>
+      <c r="M651" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="652" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A652" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B652" s="1">
+        <v>4</v>
+      </c>
+      <c r="C652" t="s">
+        <v>129</v>
+      </c>
+      <c r="D652">
+        <v>51</v>
+      </c>
+      <c r="E652" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F652" t="s">
+        <v>318</v>
+      </c>
+      <c r="G652" t="str">
+        <f>VLOOKUP(F652,Sayfa2!A:B,2,0)</f>
+        <v>cc4fdbe7-c46e-41e7-8047-29793bccfdd0</v>
+      </c>
+      <c r="H652" t="s">
+        <v>45</v>
+      </c>
+      <c r="I652">
+        <f>VLOOKUP(H652,Sayfa2!$H$132:$I$172,2,0)</f>
+        <v>33</v>
+      </c>
+      <c r="J652" s="1">
+        <v>1</v>
+      </c>
+      <c r="K652">
+        <v>2</v>
+      </c>
+      <c r="L652" s="1">
+        <v>10</v>
+      </c>
+      <c r="M652" t="s">
+        <v>128</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M488" xr:uid="{2D6820A2-C4B6-4EF0-94DD-4395E6273D53}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -24538,9 +31687,6 @@
         <filter val="e8b38ebc-0c41-4bdf-b228-f3ba7d136dd0"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G2:J180">
-      <sortCondition ref="G1"/>
-    </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Rangesayacv7.xlsx
+++ b/Rangesayacv7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\Downloads\IpekyolRangeSayac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A4DFCC-B86B-4588-9AC8-01EDB6C487DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E3F97A-9DDC-4C75-8FD4-691A37C2F2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{586848BF-8DA1-41BE-9680-FDF5F1E34B0D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{586848BF-8DA1-41BE-9680-FDF5F1E34B0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$M$652</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$M$918</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sayfa2!$G$1:$J$180</definedName>
     <definedName name="ara">IF(ISERROR(VLOOKUP([1]!Tablo_PRODYOLURT2012_kaynağından_sorgula4[[#This Row],[Ops]],[1]Resimsiz!XFD:A,2,0)),"yok",IF(VLOOKUP([1]!Tablo_PRODYOLURT2012_kaynağından_sorgula4[[#This Row],[Ops]],[1]Resimsiz!XFD:A,2,0)="","var",VLOOKUP([1]!Tablo_PRODYOLURT2012_kaynağından_sorgula4[[#This Row],[Ops]],[1]Resimsiz!XFD:A,2,0)))</definedName>
     <definedName name="mu">IF(ISERROR(VLOOKUP(#REF!,#REF!,2,0)),"yok",IF(VLOOKUP(#REF!,#REF!,2,0)="","var",VLOOKUP(#REF!,#REF!,2,0)))</definedName>
@@ -1760,6 +1760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6820A2-C4B6-4EF0-94DD-4395E6273D53}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M918"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1817,7 +1818,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1858,7 +1859,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1899,7 +1900,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1940,7 +1941,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1981,7 +1982,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -2022,7 +2023,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -2063,7 +2064,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -2104,7 +2105,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -2145,7 +2146,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -2186,7 +2187,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -2227,7 +2228,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -2268,7 +2269,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -2309,7 +2310,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -2350,7 +2351,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -2391,7 +2392,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
@@ -2432,7 +2433,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -2473,7 +2474,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -2514,7 +2515,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
@@ -2555,7 +2556,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
@@ -2596,7 +2597,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
@@ -2637,7 +2638,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
@@ -2678,7 +2679,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
@@ -2719,7 +2720,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
@@ -2760,7 +2761,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
@@ -2801,7 +2802,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
@@ -2842,7 +2843,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
@@ -2883,7 +2884,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
@@ -2924,7 +2925,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
@@ -2965,7 +2966,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>5</v>
       </c>
@@ -3006,7 +3007,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -3047,7 +3048,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>5</v>
       </c>
@@ -3088,7 +3089,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>5</v>
       </c>
@@ -3129,7 +3130,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
@@ -3170,7 +3171,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
@@ -3211,7 +3212,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>5</v>
       </c>
@@ -3252,7 +3253,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
@@ -3293,7 +3294,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
@@ -3334,7 +3335,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
@@ -3375,7 +3376,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
@@ -3416,7 +3417,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
@@ -3457,7 +3458,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>5</v>
       </c>
@@ -3498,7 +3499,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
@@ -3539,7 +3540,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>5</v>
       </c>
@@ -3580,7 +3581,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>5</v>
       </c>
@@ -3621,7 +3622,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>5</v>
       </c>
@@ -3662,7 +3663,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>5</v>
       </c>
@@ -3703,7 +3704,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>5</v>
       </c>
@@ -3744,7 +3745,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>5</v>
       </c>
@@ -3785,7 +3786,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>5</v>
       </c>
@@ -3826,7 +3827,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
@@ -3867,7 +3868,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>5</v>
       </c>
@@ -3908,7 +3909,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>5</v>
       </c>
@@ -3949,7 +3950,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>5</v>
       </c>
@@ -3990,7 +3991,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>5</v>
       </c>
@@ -4031,7 +4032,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>5</v>
       </c>
@@ -4072,7 +4073,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>5</v>
       </c>
@@ -4113,7 +4114,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>5</v>
       </c>
@@ -4154,7 +4155,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>5</v>
       </c>
@@ -4195,7 +4196,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>5</v>
       </c>
@@ -4236,7 +4237,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>5</v>
       </c>
@@ -4277,7 +4278,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>5</v>
       </c>
@@ -4318,7 +4319,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>5</v>
       </c>
@@ -4359,7 +4360,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>5</v>
       </c>
@@ -4400,7 +4401,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>5</v>
       </c>
@@ -4441,7 +4442,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>5</v>
       </c>
@@ -4482,7 +4483,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>5</v>
       </c>
@@ -4523,7 +4524,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>5</v>
       </c>
@@ -4564,7 +4565,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>5</v>
       </c>
@@ -4605,7 +4606,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>5</v>
       </c>
@@ -4646,7 +4647,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>5</v>
       </c>
@@ -4687,7 +4688,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>5</v>
       </c>
@@ -4728,7 +4729,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>5</v>
       </c>
@@ -4769,7 +4770,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>5</v>
       </c>
@@ -4810,7 +4811,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>5</v>
       </c>
@@ -4851,7 +4852,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>5</v>
       </c>
@@ -4892,7 +4893,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>5</v>
       </c>
@@ -4933,7 +4934,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>5</v>
       </c>
@@ -4974,7 +4975,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>5</v>
       </c>
@@ -5015,7 +5016,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>5</v>
       </c>
@@ -5056,7 +5057,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>5</v>
       </c>
@@ -5097,7 +5098,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>5</v>
       </c>
@@ -5138,7 +5139,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>5</v>
       </c>
@@ -5179,7 +5180,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>5</v>
       </c>
@@ -5220,7 +5221,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>5</v>
       </c>
@@ -5261,7 +5262,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>5</v>
       </c>
@@ -5302,7 +5303,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>5</v>
       </c>
@@ -5343,7 +5344,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>5</v>
       </c>
@@ -5384,7 +5385,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>5</v>
       </c>
@@ -5425,7 +5426,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>5</v>
       </c>
@@ -5466,7 +5467,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>5</v>
       </c>
@@ -5507,7 +5508,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>5</v>
       </c>
@@ -5548,7 +5549,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>5</v>
       </c>
@@ -5589,7 +5590,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>5</v>
       </c>
@@ -5630,7 +5631,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>5</v>
       </c>
@@ -5671,7 +5672,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>5</v>
       </c>
@@ -5712,7 +5713,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>5</v>
       </c>
@@ -5753,7 +5754,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>5</v>
       </c>
@@ -5794,7 +5795,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>5</v>
       </c>
@@ -5835,7 +5836,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>5</v>
       </c>
@@ -5876,7 +5877,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>5</v>
       </c>
@@ -5917,7 +5918,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>5</v>
       </c>
@@ -5958,7 +5959,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>5</v>
       </c>
@@ -5999,7 +6000,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>5</v>
       </c>
@@ -6040,7 +6041,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>5</v>
       </c>
@@ -6081,7 +6082,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>5</v>
       </c>
@@ -6122,7 +6123,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>5</v>
       </c>
@@ -6163,7 +6164,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>5</v>
       </c>
@@ -6204,7 +6205,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>5</v>
       </c>
@@ -6245,7 +6246,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>5</v>
       </c>
@@ -6286,7 +6287,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>5</v>
       </c>
@@ -6327,7 +6328,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>5</v>
       </c>
@@ -6368,7 +6369,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>5</v>
       </c>
@@ -6409,7 +6410,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>5</v>
       </c>
@@ -6450,7 +6451,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>5</v>
       </c>
@@ -6491,7 +6492,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>5</v>
       </c>
@@ -6532,7 +6533,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>5</v>
       </c>
@@ -6573,7 +6574,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>5</v>
       </c>
@@ -6614,7 +6615,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>5</v>
       </c>
@@ -6655,7 +6656,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>5</v>
       </c>
@@ -6696,7 +6697,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>5</v>
       </c>
@@ -6737,7 +6738,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>5</v>
       </c>
@@ -6778,7 +6779,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>5</v>
       </c>
@@ -6819,7 +6820,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>5</v>
       </c>
@@ -6860,7 +6861,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>5</v>
       </c>
@@ -6901,7 +6902,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>5</v>
       </c>
@@ -6942,7 +6943,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>5</v>
       </c>
@@ -6983,7 +6984,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>5</v>
       </c>
@@ -7024,7 +7025,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>5</v>
       </c>
@@ -7065,7 +7066,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>5</v>
       </c>
@@ -7106,7 +7107,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>5</v>
       </c>
@@ -7147,7 +7148,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>5</v>
       </c>
@@ -7188,7 +7189,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>5</v>
       </c>
@@ -7229,7 +7230,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>5</v>
       </c>
@@ -7270,7 +7271,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>5</v>
       </c>
@@ -7311,7 +7312,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>5</v>
       </c>
@@ -7352,7 +7353,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>5</v>
       </c>
@@ -7393,7 +7394,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>5</v>
       </c>
@@ -7434,7 +7435,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>5</v>
       </c>
@@ -7475,7 +7476,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>5</v>
       </c>
@@ -7516,7 +7517,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>5</v>
       </c>
@@ -7557,7 +7558,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>5</v>
       </c>
@@ -7598,7 +7599,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>5</v>
       </c>
@@ -7639,7 +7640,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>5</v>
       </c>
@@ -7680,7 +7681,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>5</v>
       </c>
@@ -7721,7 +7722,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>5</v>
       </c>
@@ -7762,7 +7763,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>5</v>
       </c>
@@ -7803,7 +7804,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>5</v>
       </c>
@@ -7844,7 +7845,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>5</v>
       </c>
@@ -7885,7 +7886,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>5</v>
       </c>
@@ -7926,7 +7927,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>5</v>
       </c>
@@ -7967,7 +7968,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>5</v>
       </c>
@@ -8008,7 +8009,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>5</v>
       </c>
@@ -8049,7 +8050,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>5</v>
       </c>
@@ -8090,7 +8091,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>5</v>
       </c>
@@ -8131,7 +8132,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>5</v>
       </c>
@@ -8172,7 +8173,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>5</v>
       </c>
@@ -8213,7 +8214,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>5</v>
       </c>
@@ -8254,7 +8255,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>5</v>
       </c>
@@ -8295,7 +8296,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>5</v>
       </c>
@@ -8336,7 +8337,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>5</v>
       </c>
@@ -8377,7 +8378,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>5</v>
       </c>
@@ -8418,7 +8419,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>5</v>
       </c>
@@ -8459,7 +8460,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>5</v>
       </c>
@@ -8500,7 +8501,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>5</v>
       </c>
@@ -8541,7 +8542,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>5</v>
       </c>
@@ -8582,7 +8583,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>5</v>
       </c>
@@ -8623,7 +8624,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>5</v>
       </c>
@@ -8664,7 +8665,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>5</v>
       </c>
@@ -8705,7 +8706,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>5</v>
       </c>
@@ -8746,7 +8747,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>5</v>
       </c>
@@ -8787,7 +8788,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>5</v>
       </c>
@@ -8828,7 +8829,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>5</v>
       </c>
@@ -8869,7 +8870,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>5</v>
       </c>
@@ -8910,7 +8911,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>5</v>
       </c>
@@ -8951,7 +8952,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>5</v>
       </c>
@@ -8992,7 +8993,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>5</v>
       </c>
@@ -9033,7 +9034,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>5</v>
       </c>
@@ -9074,7 +9075,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>5</v>
       </c>
@@ -9115,7 +9116,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>5</v>
       </c>
@@ -9156,7 +9157,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>5</v>
       </c>
@@ -9197,7 +9198,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>5</v>
       </c>
@@ -9238,7 +9239,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>5</v>
       </c>
@@ -9279,7 +9280,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>5</v>
       </c>
@@ -9320,7 +9321,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>5</v>
       </c>
@@ -9361,7 +9362,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>5</v>
       </c>
@@ -9402,7 +9403,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>5</v>
       </c>
@@ -9443,7 +9444,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>5</v>
       </c>
@@ -9484,7 +9485,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>5</v>
       </c>
@@ -9525,7 +9526,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>5</v>
       </c>
@@ -9566,7 +9567,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>5</v>
       </c>
@@ -9607,7 +9608,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>88</v>
       </c>
@@ -9648,7 +9649,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>88</v>
       </c>
@@ -9689,7 +9690,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>88</v>
       </c>
@@ -9730,7 +9731,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>88</v>
       </c>
@@ -9771,7 +9772,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>88</v>
       </c>
@@ -9812,7 +9813,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>88</v>
       </c>
@@ -9853,7 +9854,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>88</v>
       </c>
@@ -9894,7 +9895,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>88</v>
       </c>
@@ -9935,7 +9936,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>88</v>
       </c>
@@ -9976,7 +9977,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>88</v>
       </c>
@@ -10017,7 +10018,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>88</v>
       </c>
@@ -10058,7 +10059,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>88</v>
       </c>
@@ -10099,7 +10100,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>88</v>
       </c>
@@ -10140,7 +10141,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>88</v>
       </c>
@@ -10181,7 +10182,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>88</v>
       </c>
@@ -10222,7 +10223,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>88</v>
       </c>
@@ -10263,7 +10264,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>88</v>
       </c>
@@ -10304,7 +10305,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>88</v>
       </c>
@@ -10345,7 +10346,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>88</v>
       </c>
@@ -10386,7 +10387,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>88</v>
       </c>
@@ -10427,7 +10428,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>88</v>
       </c>
@@ -10468,7 +10469,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>88</v>
       </c>
@@ -10509,7 +10510,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>88</v>
       </c>
@@ -10550,7 +10551,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>88</v>
       </c>
@@ -10591,7 +10592,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>88</v>
       </c>
@@ -10632,7 +10633,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>88</v>
       </c>
@@ -10673,7 +10674,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>88</v>
       </c>
@@ -10714,7 +10715,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>88</v>
       </c>
@@ -10755,7 +10756,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>88</v>
       </c>
@@ -10796,7 +10797,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>88</v>
       </c>
@@ -10837,7 +10838,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>88</v>
       </c>
@@ -10878,7 +10879,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>88</v>
       </c>
@@ -10919,7 +10920,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>88</v>
       </c>
@@ -10960,7 +10961,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>88</v>
       </c>
@@ -11001,7 +11002,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>88</v>
       </c>
@@ -11042,7 +11043,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>88</v>
       </c>
@@ -11083,7 +11084,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>88</v>
       </c>
@@ -11124,7 +11125,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>88</v>
       </c>
@@ -11165,7 +11166,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>88</v>
       </c>
@@ -11206,7 +11207,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>88</v>
       </c>
@@ -11247,7 +11248,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>88</v>
       </c>
@@ -11288,7 +11289,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>88</v>
       </c>
@@ -11329,7 +11330,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>88</v>
       </c>
@@ -11370,7 +11371,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>88</v>
       </c>
@@ -11411,7 +11412,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>88</v>
       </c>
@@ -11452,7 +11453,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>88</v>
       </c>
@@ -11493,7 +11494,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>88</v>
       </c>
@@ -11534,7 +11535,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>88</v>
       </c>
@@ -11575,7 +11576,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>88</v>
       </c>
@@ -11616,7 +11617,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>88</v>
       </c>
@@ -11657,7 +11658,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>88</v>
       </c>
@@ -11698,7 +11699,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>88</v>
       </c>
@@ -11739,7 +11740,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>88</v>
       </c>
@@ -11780,7 +11781,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>88</v>
       </c>
@@ -11821,7 +11822,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>88</v>
       </c>
@@ -11862,7 +11863,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>88</v>
       </c>
@@ -11903,7 +11904,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>88</v>
       </c>
@@ -11944,7 +11945,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>88</v>
       </c>
@@ -11985,7 +11986,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>88</v>
       </c>
@@ -12026,7 +12027,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>88</v>
       </c>
@@ -12067,7 +12068,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>88</v>
       </c>
@@ -12108,7 +12109,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>88</v>
       </c>
@@ -12149,7 +12150,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>88</v>
       </c>
@@ -12190,7 +12191,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>88</v>
       </c>
@@ -12231,7 +12232,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>88</v>
       </c>
@@ -12272,7 +12273,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>88</v>
       </c>
@@ -12313,7 +12314,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>88</v>
       </c>
@@ -12354,7 +12355,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>88</v>
       </c>
@@ -12395,7 +12396,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>88</v>
       </c>
@@ -12436,7 +12437,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>88</v>
       </c>
@@ -12477,7 +12478,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>88</v>
       </c>
@@ -12518,7 +12519,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>88</v>
       </c>
@@ -12559,7 +12560,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>88</v>
       </c>
@@ -12600,7 +12601,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>88</v>
       </c>
@@ -12641,7 +12642,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>88</v>
       </c>
@@ -12682,7 +12683,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>88</v>
       </c>
@@ -12723,7 +12724,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>88</v>
       </c>
@@ -12764,7 +12765,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>88</v>
       </c>
@@ -12805,7 +12806,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>88</v>
       </c>
@@ -12846,7 +12847,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>88</v>
       </c>
@@ -12887,7 +12888,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>88</v>
       </c>
@@ -12928,7 +12929,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>88</v>
       </c>
@@ -12969,7 +12970,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>88</v>
       </c>
@@ -13010,7 +13011,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>88</v>
       </c>
@@ -13051,7 +13052,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>88</v>
       </c>
@@ -13092,7 +13093,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>88</v>
       </c>
@@ -13133,7 +13134,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>88</v>
       </c>
@@ -13174,7 +13175,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>88</v>
       </c>
@@ -13215,7 +13216,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>88</v>
       </c>
@@ -13256,7 +13257,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>88</v>
       </c>
@@ -13297,7 +13298,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>88</v>
       </c>
@@ -13338,7 +13339,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>88</v>
       </c>
@@ -13379,7 +13380,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>88</v>
       </c>
@@ -13420,7 +13421,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>88</v>
       </c>
@@ -13461,7 +13462,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>88</v>
       </c>
@@ -13502,7 +13503,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>88</v>
       </c>
@@ -13543,7 +13544,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>88</v>
       </c>
@@ -13584,7 +13585,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>88</v>
       </c>
@@ -13625,7 +13626,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>88</v>
       </c>
@@ -13666,7 +13667,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>88</v>
       </c>
@@ -13707,7 +13708,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>88</v>
       </c>
@@ -13748,7 +13749,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>88</v>
       </c>
@@ -13789,7 +13790,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>88</v>
       </c>
@@ -13830,7 +13831,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>88</v>
       </c>
@@ -13871,7 +13872,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>88</v>
       </c>
@@ -13912,7 +13913,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>88</v>
       </c>
@@ -13953,7 +13954,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>88</v>
       </c>
@@ -13994,7 +13995,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>88</v>
       </c>
@@ -14035,7 +14036,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>88</v>
       </c>
@@ -14048,8 +14049,8 @@
       <c r="D300" s="1">
         <v>47</v>
       </c>
-      <c r="E300" s="1" t="s">
-        <v>7</v>
+      <c r="E300" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>39</v>
@@ -14076,7 +14077,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>88</v>
       </c>
@@ -14089,8 +14090,8 @@
       <c r="D301" s="1">
         <v>47</v>
       </c>
-      <c r="E301" s="1" t="s">
-        <v>7</v>
+      <c r="E301" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>39</v>
@@ -14117,7 +14118,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>88</v>
       </c>
@@ -14130,8 +14131,8 @@
       <c r="D302" s="1">
         <v>47</v>
       </c>
-      <c r="E302" s="1" t="s">
-        <v>7</v>
+      <c r="E302" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>39</v>
@@ -14158,7 +14159,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>88</v>
       </c>
@@ -14171,8 +14172,8 @@
       <c r="D303" s="1">
         <v>47</v>
       </c>
-      <c r="E303" s="1" t="s">
-        <v>7</v>
+      <c r="E303" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>39</v>
@@ -14199,7 +14200,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>88</v>
       </c>
@@ -14212,8 +14213,8 @@
       <c r="D304" s="1">
         <v>47</v>
       </c>
-      <c r="E304" s="1" t="s">
-        <v>7</v>
+      <c r="E304" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>39</v>
@@ -14240,7 +14241,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>88</v>
       </c>
@@ -14253,8 +14254,8 @@
       <c r="D305" s="1">
         <v>47</v>
       </c>
-      <c r="E305" s="1" t="s">
-        <v>7</v>
+      <c r="E305" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>39</v>
@@ -14281,7 +14282,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>88</v>
       </c>
@@ -14294,8 +14295,8 @@
       <c r="D306" s="1">
         <v>47</v>
       </c>
-      <c r="E306" s="1" t="s">
-        <v>7</v>
+      <c r="E306" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>39</v>
@@ -14335,8 +14336,8 @@
       <c r="D307" s="1">
         <v>47</v>
       </c>
-      <c r="E307" s="1" t="s">
-        <v>10</v>
+      <c r="E307" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>15</v>
@@ -14376,8 +14377,8 @@
       <c r="D308" s="1">
         <v>47</v>
       </c>
-      <c r="E308" s="1" t="s">
-        <v>10</v>
+      <c r="E308" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>15</v>
@@ -14417,8 +14418,8 @@
       <c r="D309" s="1">
         <v>47</v>
       </c>
-      <c r="E309" s="1" t="s">
-        <v>10</v>
+      <c r="E309" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>15</v>
@@ -14458,8 +14459,8 @@
       <c r="D310" s="1">
         <v>47</v>
       </c>
-      <c r="E310" s="1" t="s">
-        <v>10</v>
+      <c r="E310" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>15</v>
@@ -14486,7 +14487,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>88</v>
       </c>
@@ -14499,8 +14500,8 @@
       <c r="D311" s="1">
         <v>47</v>
       </c>
-      <c r="E311" s="1" t="s">
-        <v>14</v>
+      <c r="E311" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>62</v>
@@ -14527,7 +14528,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>88</v>
       </c>
@@ -14540,8 +14541,8 @@
       <c r="D312" s="1">
         <v>47</v>
       </c>
-      <c r="E312" s="1" t="s">
-        <v>14</v>
+      <c r="E312" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>62</v>
@@ -14568,7 +14569,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>88</v>
       </c>
@@ -14581,8 +14582,8 @@
       <c r="D313" s="1">
         <v>47</v>
       </c>
-      <c r="E313" s="1" t="s">
-        <v>14</v>
+      <c r="E313" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>62</v>
@@ -14609,7 +14610,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>88</v>
       </c>
@@ -14622,8 +14623,8 @@
       <c r="D314" s="1">
         <v>47</v>
       </c>
-      <c r="E314" s="1" t="s">
-        <v>14</v>
+      <c r="E314" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>62</v>
@@ -14650,7 +14651,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>88</v>
       </c>
@@ -14663,8 +14664,8 @@
       <c r="D315" s="1">
         <v>47</v>
       </c>
-      <c r="E315" s="1" t="s">
-        <v>14</v>
+      <c r="E315" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>62</v>
@@ -14691,7 +14692,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>88</v>
       </c>
@@ -14704,8 +14705,8 @@
       <c r="D316" s="1">
         <v>47</v>
       </c>
-      <c r="E316" s="1" t="s">
-        <v>14</v>
+      <c r="E316" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>62</v>
@@ -14732,7 +14733,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>88</v>
       </c>
@@ -14773,7 +14774,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>88</v>
       </c>
@@ -14814,7 +14815,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>88</v>
       </c>
@@ -14855,7 +14856,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>88</v>
       </c>
@@ -14896,7 +14897,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>88</v>
       </c>
@@ -14937,7 +14938,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>88</v>
       </c>
@@ -14978,7 +14979,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>88</v>
       </c>
@@ -15019,7 +15020,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>88</v>
       </c>
@@ -15060,7 +15061,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>88</v>
       </c>
@@ -15101,7 +15102,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>88</v>
       </c>
@@ -15142,7 +15143,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>88</v>
       </c>
@@ -15183,7 +15184,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>88</v>
       </c>
@@ -15224,7 +15225,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>88</v>
       </c>
@@ -15265,7 +15266,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>88</v>
       </c>
@@ -15306,7 +15307,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>88</v>
       </c>
@@ -15347,7 +15348,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>88</v>
       </c>
@@ -15388,7 +15389,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>88</v>
       </c>
@@ -15429,7 +15430,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>88</v>
       </c>
@@ -15470,7 +15471,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>88</v>
       </c>
@@ -15511,7 +15512,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>88</v>
       </c>
@@ -15552,7 +15553,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>88</v>
       </c>
@@ -15593,7 +15594,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>88</v>
       </c>
@@ -15634,7 +15635,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>88</v>
       </c>
@@ -15675,7 +15676,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>88</v>
       </c>
@@ -15716,7 +15717,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>88</v>
       </c>
@@ -15757,7 +15758,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>88</v>
       </c>
@@ -15798,7 +15799,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>88</v>
       </c>
@@ -15839,7 +15840,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>88</v>
       </c>
@@ -15880,7 +15881,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>88</v>
       </c>
@@ -15921,7 +15922,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>88</v>
       </c>
@@ -15962,7 +15963,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>88</v>
       </c>
@@ -16003,7 +16004,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>88</v>
       </c>
@@ -16044,7 +16045,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>88</v>
       </c>
@@ -16085,7 +16086,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>88</v>
       </c>
@@ -16126,7 +16127,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>88</v>
       </c>
@@ -16167,7 +16168,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>88</v>
       </c>
@@ -16208,7 +16209,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>88</v>
       </c>
@@ -16252,7 +16253,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>88</v>
       </c>
@@ -16296,7 +16297,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>88</v>
       </c>
@@ -16340,7 +16341,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>88</v>
       </c>
@@ -16384,7 +16385,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>88</v>
       </c>
@@ -16428,7 +16429,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>88</v>
       </c>
@@ -16470,7 +16471,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>88</v>
       </c>
@@ -16514,7 +16515,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>88</v>
       </c>
@@ -16558,7 +16559,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>88</v>
       </c>
@@ -16602,7 +16603,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>88</v>
       </c>
@@ -16646,7 +16647,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>88</v>
       </c>
@@ -16690,7 +16691,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>88</v>
       </c>
@@ -16734,7 +16735,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>88</v>
       </c>
@@ -16778,7 +16779,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>88</v>
       </c>
@@ -16822,7 +16823,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>88</v>
       </c>
@@ -16866,7 +16867,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>88</v>
       </c>
@@ -16910,7 +16911,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>88</v>
       </c>
@@ -16954,7 +16955,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>88</v>
       </c>
@@ -16998,7 +16999,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>88</v>
       </c>
@@ -17042,7 +17043,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>88</v>
       </c>
@@ -17086,7 +17087,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>88</v>
       </c>
@@ -17130,7 +17131,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>88</v>
       </c>
@@ -17172,7 +17173,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>88</v>
       </c>
@@ -17216,7 +17217,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>88</v>
       </c>
@@ -17260,7 +17261,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>88</v>
       </c>
@@ -17304,7 +17305,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>88</v>
       </c>
@@ -17348,7 +17349,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>88</v>
       </c>
@@ -17392,7 +17393,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>88</v>
       </c>
@@ -17436,7 +17437,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>88</v>
       </c>
@@ -17480,7 +17481,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>88</v>
       </c>
@@ -17524,7 +17525,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>88</v>
       </c>
@@ -17566,7 +17567,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>88</v>
       </c>
@@ -17610,7 +17611,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>88</v>
       </c>
@@ -17652,7 +17653,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>88</v>
       </c>
@@ -17696,7 +17697,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>88</v>
       </c>
@@ -17740,7 +17741,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>88</v>
       </c>
@@ -17782,7 +17783,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>88</v>
       </c>
@@ -17826,7 +17827,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>88</v>
       </c>
@@ -17870,7 +17871,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>88</v>
       </c>
@@ -17914,7 +17915,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>88</v>
       </c>
@@ -17958,7 +17959,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>88</v>
       </c>
@@ -18002,7 +18003,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>88</v>
       </c>
@@ -18044,7 +18045,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>88</v>
       </c>
@@ -18088,7 +18089,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>88</v>
       </c>
@@ -18132,7 +18133,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>88</v>
       </c>
@@ -18176,7 +18177,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>88</v>
       </c>
@@ -18220,7 +18221,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>88</v>
       </c>
@@ -18264,7 +18265,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>88</v>
       </c>
@@ -18308,7 +18309,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>88</v>
       </c>
@@ -18352,7 +18353,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>88</v>
       </c>
@@ -18396,7 +18397,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>88</v>
       </c>
@@ -18440,7 +18441,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>88</v>
       </c>
@@ -18484,7 +18485,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>88</v>
       </c>
@@ -18526,7 +18527,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>88</v>
       </c>
@@ -18570,7 +18571,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>88</v>
       </c>
@@ -18614,7 +18615,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>88</v>
       </c>
@@ -18656,7 +18657,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>88</v>
       </c>
@@ -18700,7 +18701,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>88</v>
       </c>
@@ -18744,7 +18745,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>88</v>
       </c>
@@ -18788,7 +18789,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>88</v>
       </c>
@@ -18832,7 +18833,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>88</v>
       </c>
@@ -18874,7 +18875,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>88</v>
       </c>
@@ -18916,7 +18917,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>88</v>
       </c>
@@ -18957,7 +18958,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>88</v>
       </c>
@@ -19000,7 +19001,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>88</v>
       </c>
@@ -19043,7 +19044,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>88</v>
       </c>
@@ -19086,7 +19087,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>88</v>
       </c>
@@ -19130,7 +19131,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>88</v>
       </c>
@@ -19172,7 +19173,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>88</v>
       </c>
@@ -19216,7 +19217,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>88</v>
       </c>
@@ -19260,7 +19261,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>88</v>
       </c>
@@ -19304,7 +19305,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>88</v>
       </c>
@@ -19348,7 +19349,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>88</v>
       </c>
@@ -19392,7 +19393,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>88</v>
       </c>
@@ -19434,7 +19435,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>88</v>
       </c>
@@ -19476,7 +19477,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>88</v>
       </c>
@@ -19520,7 +19521,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>88</v>
       </c>
@@ -19564,7 +19565,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>88</v>
       </c>
@@ -19608,7 +19609,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>88</v>
       </c>
@@ -19650,7 +19651,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>88</v>
       </c>
@@ -19694,7 +19695,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>88</v>
       </c>
@@ -19738,7 +19739,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>88</v>
       </c>
@@ -19782,7 +19783,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>88</v>
       </c>
@@ -19826,7 +19827,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>88</v>
       </c>
@@ -19870,7 +19871,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>88</v>
       </c>
@@ -19914,7 +19915,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>88</v>
       </c>
@@ -19958,7 +19959,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>88</v>
       </c>
@@ -20002,7 +20003,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>88</v>
       </c>
@@ -20044,7 +20045,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>88</v>
       </c>
@@ -20086,7 +20087,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>88</v>
       </c>
@@ -20130,7 +20131,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>88</v>
       </c>
@@ -20174,7 +20175,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>88</v>
       </c>
@@ -20218,7 +20219,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>88</v>
       </c>
@@ -20261,7 +20262,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>88</v>
       </c>
@@ -20305,7 +20306,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>88</v>
       </c>
@@ -20349,7 +20350,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>88</v>
       </c>
@@ -20391,7 +20392,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>88</v>
       </c>
@@ -20435,7 +20436,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>88</v>
       </c>
@@ -20477,7 +20478,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>88</v>
       </c>
@@ -20519,7 +20520,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>88</v>
       </c>
@@ -20563,7 +20564,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>88</v>
       </c>
@@ -20606,7 +20607,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>88</v>
       </c>
@@ -20649,7 +20650,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>88</v>
       </c>
@@ -20692,7 +20693,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>88</v>
       </c>
@@ -20733,7 +20734,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>88</v>
       </c>
@@ -20777,7 +20778,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>88</v>
       </c>
@@ -20821,7 +20822,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>88</v>
       </c>
@@ -20865,7 +20866,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>88</v>
       </c>
@@ -20909,7 +20910,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>88</v>
       </c>
@@ -20951,7 +20952,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>88</v>
       </c>
@@ -20993,7 +20994,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>88</v>
       </c>
@@ -21035,7 +21036,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>88</v>
       </c>
@@ -21079,7 +21080,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>88</v>
       </c>
@@ -21121,7 +21122,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>88</v>
       </c>
@@ -21383,7 +21384,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>88</v>
       </c>
@@ -21426,7 +21427,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>88</v>
       </c>
@@ -21469,7 +21470,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>88</v>
       </c>
@@ -21512,7 +21513,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>88</v>
       </c>
@@ -21555,7 +21556,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>88</v>
       </c>
@@ -21598,7 +21599,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>88</v>
       </c>
@@ -21641,7 +21642,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>88</v>
       </c>
@@ -21682,7 +21683,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>88</v>
       </c>
@@ -21723,7 +21724,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>88</v>
       </c>
@@ -21764,7 +21765,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>88</v>
       </c>
@@ -21807,7 +21808,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>88</v>
       </c>
@@ -21850,7 +21851,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>88</v>
       </c>
@@ -21893,7 +21894,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>88</v>
       </c>
@@ -21936,7 +21937,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>88</v>
       </c>
@@ -21979,7 +21980,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>88</v>
       </c>
@@ -22022,7 +22023,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>88</v>
       </c>
@@ -22065,7 +22066,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>88</v>
       </c>
@@ -22108,7 +22109,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>5</v>
       </c>
@@ -22152,7 +22153,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>5</v>
       </c>
@@ -22196,7 +22197,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>5</v>
       </c>
@@ -22240,7 +22241,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>5</v>
       </c>
@@ -22284,7 +22285,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>5</v>
       </c>
@@ -22328,7 +22329,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>5</v>
       </c>
@@ -22369,7 +22370,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>5</v>
       </c>
@@ -22413,7 +22414,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>5</v>
       </c>
@@ -22454,7 +22455,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>5</v>
       </c>
@@ -22498,7 +22499,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>5</v>
       </c>
@@ -22542,7 +22543,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>5</v>
       </c>
@@ -22586,7 +22587,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>5</v>
       </c>
@@ -22630,7 +22631,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>5</v>
       </c>
@@ -22674,7 +22675,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>5</v>
       </c>
@@ -22718,7 +22719,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>5</v>
       </c>
@@ -22762,7 +22763,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>5</v>
       </c>
@@ -22806,7 +22807,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>5</v>
       </c>
@@ -22850,7 +22851,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>5</v>
       </c>
@@ -22894,7 +22895,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>5</v>
       </c>
@@ -22938,7 +22939,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>5</v>
       </c>
@@ -22982,7 +22983,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>5</v>
       </c>
@@ -23026,7 +23027,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>5</v>
       </c>
@@ -23070,7 +23071,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>5</v>
       </c>
@@ -23114,7 +23115,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>5</v>
       </c>
@@ -23158,7 +23159,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>5</v>
       </c>
@@ -23202,7 +23203,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>5</v>
       </c>
@@ -23243,7 +23244,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>5</v>
       </c>
@@ -23287,7 +23288,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>5</v>
       </c>
@@ -23331,7 +23332,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>5</v>
       </c>
@@ -23372,7 +23373,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>5</v>
       </c>
@@ -23416,7 +23417,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>5</v>
       </c>
@@ -23460,7 +23461,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>5</v>
       </c>
@@ -23504,7 +23505,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>5</v>
       </c>
@@ -23548,7 +23549,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>5</v>
       </c>
@@ -23592,7 +23593,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>5</v>
       </c>
@@ -23636,7 +23637,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>5</v>
       </c>
@@ -23680,7 +23681,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>5</v>
       </c>
@@ -23724,7 +23725,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>5</v>
       </c>
@@ -23768,7 +23769,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>5</v>
       </c>
@@ -23812,7 +23813,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>5</v>
       </c>
@@ -23856,7 +23857,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>5</v>
       </c>
@@ -23900,7 +23901,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>5</v>
       </c>
@@ -23944,7 +23945,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>5</v>
       </c>
@@ -23988,7 +23989,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>5</v>
       </c>
@@ -24032,7 +24033,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>5</v>
       </c>
@@ -24076,7 +24077,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>5</v>
       </c>
@@ -24120,7 +24121,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>5</v>
       </c>
@@ -24161,7 +24162,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>5</v>
       </c>
@@ -24202,7 +24203,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>5</v>
       </c>
@@ -24246,7 +24247,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>5</v>
       </c>
@@ -24290,7 +24291,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>5</v>
       </c>
@@ -24334,7 +24335,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>5</v>
       </c>
@@ -24378,7 +24379,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>5</v>
       </c>
@@ -24422,7 +24423,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>5</v>
       </c>
@@ -24463,7 +24464,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>5</v>
       </c>
@@ -24507,7 +24508,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>5</v>
       </c>
@@ -24548,7 +24549,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>5</v>
       </c>
@@ -24592,7 +24593,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>5</v>
       </c>
@@ -24636,7 +24637,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>5</v>
       </c>
@@ -24680,7 +24681,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>5</v>
       </c>
@@ -24724,7 +24725,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>5</v>
       </c>
@@ -24768,7 +24769,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>5</v>
       </c>
@@ -24812,7 +24813,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>5</v>
       </c>
@@ -24856,7 +24857,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>5</v>
       </c>
@@ -24900,7 +24901,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>5</v>
       </c>
@@ -24944,7 +24945,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>5</v>
       </c>
@@ -24985,7 +24986,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>5</v>
       </c>
@@ -25029,7 +25030,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>5</v>
       </c>
@@ -25070,7 +25071,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>5</v>
       </c>
@@ -25114,7 +25115,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>5</v>
       </c>
@@ -25155,7 +25156,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>5</v>
       </c>
@@ -25199,7 +25200,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>5</v>
       </c>
@@ -25243,7 +25244,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>5</v>
       </c>
@@ -25287,7 +25288,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>5</v>
       </c>
@@ -25331,7 +25332,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>5</v>
       </c>
@@ -25375,7 +25376,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>5</v>
       </c>
@@ -25416,7 +25417,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>5</v>
       </c>
@@ -25457,7 +25458,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>5</v>
       </c>
@@ -25501,7 +25502,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>5</v>
       </c>
@@ -25545,7 +25546,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>5</v>
       </c>
@@ -25589,7 +25590,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>5</v>
       </c>
@@ -25633,7 +25634,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>5</v>
       </c>
@@ -25674,7 +25675,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>5</v>
       </c>
@@ -25715,7 +25716,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>5</v>
       </c>
@@ -25756,7 +25757,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>5</v>
       </c>
@@ -25797,7 +25798,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>5</v>
       </c>
@@ -25838,7 +25839,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>5</v>
       </c>
@@ -25882,7 +25883,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>5</v>
       </c>
@@ -25926,7 +25927,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>5</v>
       </c>
@@ -25970,7 +25971,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>5</v>
       </c>
@@ -26014,7 +26015,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>5</v>
       </c>
@@ -26058,7 +26059,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>5</v>
       </c>
@@ -26102,7 +26103,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>5</v>
       </c>
@@ -26146,7 +26147,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>5</v>
       </c>
@@ -26190,7 +26191,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>5</v>
       </c>
@@ -26234,7 +26235,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>5</v>
       </c>
@@ -26278,7 +26279,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>5</v>
       </c>
@@ -26319,7 +26320,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>5</v>
       </c>
@@ -26363,7 +26364,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>5</v>
       </c>
@@ -26404,7 +26405,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>5</v>
       </c>
@@ -26445,7 +26446,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>5</v>
       </c>
@@ -26486,7 +26487,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>5</v>
       </c>
@@ -26527,7 +26528,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>5</v>
       </c>
@@ -26568,7 +26569,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>5</v>
       </c>
@@ -26612,7 +26613,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>5</v>
       </c>
@@ -26656,7 +26657,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>5</v>
       </c>
@@ -26700,7 +26701,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>5</v>
       </c>
@@ -26744,7 +26745,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>5</v>
       </c>
@@ -26788,7 +26789,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>5</v>
       </c>
@@ -26829,7 +26830,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>5</v>
       </c>
@@ -26873,7 +26874,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>5</v>
       </c>
@@ -26917,7 +26918,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>5</v>
       </c>
@@ -26961,7 +26962,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>5</v>
       </c>
@@ -27005,7 +27006,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>5</v>
       </c>
@@ -27046,7 +27047,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>5</v>
       </c>
@@ -27090,7 +27091,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>5</v>
       </c>
@@ -27134,7 +27135,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>5</v>
       </c>
@@ -27178,7 +27179,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>5</v>
       </c>
@@ -27222,7 +27223,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>5</v>
       </c>
@@ -27266,7 +27267,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>5</v>
       </c>
@@ -27310,7 +27311,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>5</v>
       </c>
@@ -27354,7 +27355,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>5</v>
       </c>
@@ -27398,7 +27399,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>5</v>
       </c>
@@ -27439,7 +27440,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>5</v>
       </c>
@@ -27483,7 +27484,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>5</v>
       </c>
@@ -27527,7 +27528,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>5</v>
       </c>
@@ -27571,7 +27572,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>5</v>
       </c>
@@ -27615,7 +27616,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>5</v>
       </c>
@@ -27656,7 +27657,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>5</v>
       </c>
@@ -27700,7 +27701,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>5</v>
       </c>
@@ -27744,7 +27745,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>5</v>
       </c>
@@ -27788,7 +27789,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>5</v>
       </c>
@@ -27832,7 +27833,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>5</v>
       </c>
@@ -27876,7 +27877,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>5</v>
       </c>
@@ -27920,7 +27921,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>5</v>
       </c>
@@ -27964,7 +27965,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>5</v>
       </c>
@@ -28008,7 +28009,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>5</v>
       </c>
@@ -28049,7 +28050,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>5</v>
       </c>
@@ -28093,7 +28094,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>5</v>
       </c>
@@ -28137,7 +28138,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>5</v>
       </c>
@@ -28181,7 +28182,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>5</v>
       </c>
@@ -28222,7 +28223,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>5</v>
       </c>
@@ -28266,7 +28267,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>5</v>
       </c>
@@ -28310,7 +28311,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>5</v>
       </c>
@@ -28354,7 +28355,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>5</v>
       </c>
@@ -28394,7 +28395,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>5</v>
       </c>
@@ -28437,7 +28438,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>5</v>
       </c>
@@ -28480,7 +28481,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>5</v>
       </c>
@@ -28523,7 +28524,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>5</v>
       </c>
@@ -28566,7 +28567,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
         <v>5</v>
       </c>
@@ -28609,7 +28610,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
         <v>5</v>
       </c>
@@ -28649,7 +28650,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
         <v>5</v>
       </c>
@@ -28692,7 +28693,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
         <v>5</v>
       </c>
@@ -28735,7 +28736,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
         <v>5</v>
       </c>
@@ -28778,7 +28779,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
         <v>5</v>
       </c>
@@ -28821,7 +28822,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
         <v>5</v>
       </c>
@@ -28864,7 +28865,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
         <v>5</v>
       </c>
@@ -28907,7 +28908,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
         <v>5</v>
       </c>
@@ -28950,7 +28951,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
         <v>5</v>
       </c>
@@ -28993,7 +28994,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
         <v>5</v>
       </c>
@@ -29036,7 +29037,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
         <v>5</v>
       </c>
@@ -29079,7 +29080,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
         <v>5</v>
       </c>
@@ -29122,7 +29123,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
         <v>5</v>
       </c>
@@ -29165,7 +29166,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
         <v>5</v>
       </c>
@@ -29208,7 +29209,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>88</v>
       </c>
@@ -29249,7 +29250,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>88</v>
       </c>
@@ -29290,7 +29291,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>88</v>
       </c>
@@ -29331,7 +29332,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>88</v>
       </c>
@@ -29372,7 +29373,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>88</v>
       </c>
@@ -29413,7 +29414,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>88</v>
       </c>
@@ -29454,7 +29455,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>88</v>
       </c>
@@ -29495,7 +29496,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>88</v>
       </c>
@@ -29536,7 +29537,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>88</v>
       </c>
@@ -29577,7 +29578,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>88</v>
       </c>
@@ -29618,7 +29619,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>88</v>
       </c>
@@ -29659,7 +29660,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>88</v>
       </c>
@@ -29700,7 +29701,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>88</v>
       </c>
@@ -29741,7 +29742,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>88</v>
       </c>
@@ -29782,7 +29783,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>88</v>
       </c>
@@ -29823,7 +29824,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>88</v>
       </c>
@@ -29864,7 +29865,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>88</v>
       </c>
@@ -29905,7 +29906,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>88</v>
       </c>
@@ -29946,7 +29947,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>88</v>
       </c>
@@ -29987,7 +29988,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>88</v>
       </c>
@@ -30028,7 +30029,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>88</v>
       </c>
@@ -30069,7 +30070,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>88</v>
       </c>
@@ -30110,7 +30111,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>88</v>
       </c>
@@ -30151,7 +30152,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>88</v>
       </c>
@@ -30192,7 +30193,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>88</v>
       </c>
@@ -30233,7 +30234,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>88</v>
       </c>
@@ -30274,7 +30275,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>88</v>
       </c>
@@ -30315,7 +30316,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>88</v>
       </c>
@@ -30356,7 +30357,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>88</v>
       </c>
@@ -30397,7 +30398,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>88</v>
       </c>
@@ -30438,7 +30439,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>88</v>
       </c>
@@ -30479,7 +30480,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>88</v>
       </c>
@@ -30520,7 +30521,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>88</v>
       </c>
@@ -30561,7 +30562,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>88</v>
       </c>
@@ -30602,7 +30603,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>88</v>
       </c>
@@ -30643,7 +30644,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>88</v>
       </c>
@@ -30684,7 +30685,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>88</v>
       </c>
@@ -30725,7 +30726,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>88</v>
       </c>
@@ -30766,7 +30767,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>88</v>
       </c>
@@ -30807,7 +30808,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>88</v>
       </c>
@@ -30848,7 +30849,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>88</v>
       </c>
@@ -30889,7 +30890,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>88</v>
       </c>
@@ -30930,7 +30931,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>88</v>
       </c>
@@ -30971,7 +30972,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>88</v>
       </c>
@@ -31012,7 +31013,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>88</v>
       </c>
@@ -31053,7 +31054,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>88</v>
       </c>
@@ -31094,7 +31095,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>88</v>
       </c>
@@ -31135,7 +31136,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>88</v>
       </c>
@@ -31176,7 +31177,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>88</v>
       </c>
@@ -31217,7 +31218,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>88</v>
       </c>
@@ -31258,7 +31259,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>88</v>
       </c>
@@ -31299,7 +31300,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>88</v>
       </c>
@@ -31340,7 +31341,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>88</v>
       </c>
@@ -31381,7 +31382,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>88</v>
       </c>
@@ -31422,7 +31423,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>88</v>
       </c>
@@ -31463,7 +31464,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>88</v>
       </c>
@@ -31504,7 +31505,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>88</v>
       </c>
@@ -31545,7 +31546,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>88</v>
       </c>
@@ -31586,7 +31587,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>88</v>
       </c>
@@ -31627,7 +31628,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>88</v>
       </c>
@@ -31668,7 +31669,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>88</v>
       </c>
@@ -31709,7 +31710,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>88</v>
       </c>
@@ -31750,7 +31751,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>88</v>
       </c>
@@ -31791,7 +31792,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>88</v>
       </c>
@@ -31832,7 +31833,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>88</v>
       </c>
@@ -31873,7 +31874,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>88</v>
       </c>
@@ -31914,7 +31915,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>88</v>
       </c>
@@ -31955,7 +31956,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>88</v>
       </c>
@@ -31996,7 +31997,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>88</v>
       </c>
@@ -32037,7 +32038,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>88</v>
       </c>
@@ -32078,7 +32079,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>88</v>
       </c>
@@ -32119,7 +32120,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>88</v>
       </c>
@@ -32160,7 +32161,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>88</v>
       </c>
@@ -32201,7 +32202,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>88</v>
       </c>
@@ -32242,7 +32243,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>88</v>
       </c>
@@ -32283,7 +32284,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>88</v>
       </c>
@@ -32324,7 +32325,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>88</v>
       </c>
@@ -32365,7 +32366,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>88</v>
       </c>
@@ -32406,7 +32407,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>88</v>
       </c>
@@ -32447,7 +32448,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>88</v>
       </c>
@@ -32488,7 +32489,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>88</v>
       </c>
@@ -32529,7 +32530,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>88</v>
       </c>
@@ -32570,7 +32571,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>88</v>
       </c>
@@ -32734,7 +32735,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>88</v>
       </c>
@@ -32775,7 +32776,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>88</v>
       </c>
@@ -32816,7 +32817,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>88</v>
       </c>
@@ -32857,7 +32858,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>88</v>
       </c>
@@ -32898,7 +32899,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>88</v>
       </c>
@@ -32939,7 +32940,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>88</v>
       </c>
@@ -32980,7 +32981,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>88</v>
       </c>
@@ -33021,7 +33022,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>88</v>
       </c>
@@ -33062,7 +33063,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>88</v>
       </c>
@@ -33103,7 +33104,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>88</v>
       </c>
@@ -33144,7 +33145,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>88</v>
       </c>
@@ -33185,7 +33186,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>88</v>
       </c>
@@ -33226,7 +33227,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>88</v>
       </c>
@@ -33267,7 +33268,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>88</v>
       </c>
@@ -33308,7 +33309,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>88</v>
       </c>
@@ -33349,7 +33350,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>88</v>
       </c>
@@ -33390,7 +33391,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>88</v>
       </c>
@@ -33431,7 +33432,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>88</v>
       </c>
@@ -33472,7 +33473,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>88</v>
       </c>
@@ -33513,7 +33514,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>88</v>
       </c>
@@ -33554,7 +33555,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>88</v>
       </c>
@@ -33595,7 +33596,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>88</v>
       </c>
@@ -33636,7 +33637,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>88</v>
       </c>
@@ -33677,7 +33678,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>88</v>
       </c>
@@ -33718,7 +33719,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>88</v>
       </c>
@@ -33759,7 +33760,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="764" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>88</v>
       </c>
@@ -33800,7 +33801,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="765" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>88</v>
       </c>
@@ -33841,7 +33842,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="766" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>88</v>
       </c>
@@ -33882,7 +33883,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="767" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>88</v>
       </c>
@@ -33923,7 +33924,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="768" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>5</v>
       </c>
@@ -33964,7 +33965,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="769" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>5</v>
       </c>
@@ -34005,7 +34006,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="770" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>5</v>
       </c>
@@ -34046,7 +34047,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="771" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>5</v>
       </c>
@@ -34087,7 +34088,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="772" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>5</v>
       </c>
@@ -34128,7 +34129,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="773" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>5</v>
       </c>
@@ -34169,7 +34170,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="774" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>5</v>
       </c>
@@ -34210,7 +34211,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="775" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>5</v>
       </c>
@@ -34251,7 +34252,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="776" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>5</v>
       </c>
@@ -34292,7 +34293,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="777" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>5</v>
       </c>
@@ -34333,7 +34334,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="778" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>5</v>
       </c>
@@ -34374,7 +34375,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="779" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>5</v>
       </c>
@@ -34415,7 +34416,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="780" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>5</v>
       </c>
@@ -34456,7 +34457,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="781" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>5</v>
       </c>
@@ -34497,7 +34498,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="782" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>5</v>
       </c>
@@ -34538,7 +34539,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="783" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>5</v>
       </c>
@@ -34579,7 +34580,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="784" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>5</v>
       </c>
@@ -34620,7 +34621,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="785" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>5</v>
       </c>
@@ -34661,7 +34662,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="786" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>5</v>
       </c>
@@ -34702,7 +34703,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="787" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>5</v>
       </c>
@@ -34743,7 +34744,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="788" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>5</v>
       </c>
@@ -34784,7 +34785,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="789" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>5</v>
       </c>
@@ -34825,7 +34826,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="790" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>5</v>
       </c>
@@ -34866,7 +34867,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="791" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>5</v>
       </c>
@@ -34907,7 +34908,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="792" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>5</v>
       </c>
@@ -34948,7 +34949,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="793" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>5</v>
       </c>
@@ -34989,7 +34990,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="794" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>5</v>
       </c>
@@ -35030,7 +35031,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="795" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>5</v>
       </c>
@@ -35071,7 +35072,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="796" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>5</v>
       </c>
@@ -35112,7 +35113,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="797" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>5</v>
       </c>
@@ -35153,7 +35154,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="798" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>5</v>
       </c>
@@ -35194,7 +35195,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="799" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>5</v>
       </c>
@@ -35235,7 +35236,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="800" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>5</v>
       </c>
@@ -35276,7 +35277,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="801" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>5</v>
       </c>
@@ -35317,7 +35318,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="802" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>5</v>
       </c>
@@ -35358,7 +35359,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="803" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>5</v>
       </c>
@@ -35399,7 +35400,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="804" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>5</v>
       </c>
@@ -35440,7 +35441,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="805" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>5</v>
       </c>
@@ -35481,7 +35482,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="806" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>5</v>
       </c>
@@ -35522,7 +35523,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="807" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>5</v>
       </c>
@@ -35563,7 +35564,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="808" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>5</v>
       </c>
@@ -35604,7 +35605,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="809" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>5</v>
       </c>
@@ -35645,7 +35646,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="810" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>5</v>
       </c>
@@ -35686,7 +35687,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="811" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>5</v>
       </c>
@@ -35727,7 +35728,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="812" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>5</v>
       </c>
@@ -35768,7 +35769,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="813" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>5</v>
       </c>
@@ -35809,7 +35810,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="814" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>5</v>
       </c>
@@ -35850,7 +35851,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="815" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>5</v>
       </c>
@@ -35891,7 +35892,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="816" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>5</v>
       </c>
@@ -35932,7 +35933,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="817" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>5</v>
       </c>
@@ -35973,7 +35974,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="818" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>5</v>
       </c>
@@ -36014,7 +36015,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="819" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>5</v>
       </c>
@@ -36055,7 +36056,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="820" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>5</v>
       </c>
@@ -36096,7 +36097,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="821" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>5</v>
       </c>
@@ -36137,7 +36138,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="822" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>5</v>
       </c>
@@ -36178,7 +36179,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="823" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>5</v>
       </c>
@@ -36219,7 +36220,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="824" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>5</v>
       </c>
@@ -36260,7 +36261,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="825" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>5</v>
       </c>
@@ -36301,7 +36302,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="826" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>5</v>
       </c>
@@ -36342,7 +36343,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="827" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>5</v>
       </c>
@@ -36383,7 +36384,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="828" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>5</v>
       </c>
@@ -36424,7 +36425,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="829" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>5</v>
       </c>
@@ -36465,7 +36466,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="830" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>5</v>
       </c>
@@ -36506,7 +36507,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="831" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>5</v>
       </c>
@@ -36547,7 +36548,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="832" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>5</v>
       </c>
@@ -36588,7 +36589,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="833" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>5</v>
       </c>
@@ -36629,7 +36630,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="834" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>5</v>
       </c>
@@ -36670,7 +36671,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="835" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>5</v>
       </c>
@@ -36711,7 +36712,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="836" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>5</v>
       </c>
@@ -36752,7 +36753,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="837" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>5</v>
       </c>
@@ -36793,7 +36794,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="838" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>5</v>
       </c>
@@ -36834,7 +36835,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="839" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>5</v>
       </c>
@@ -36875,7 +36876,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="840" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>5</v>
       </c>
@@ -36916,7 +36917,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="841" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>5</v>
       </c>
@@ -36957,7 +36958,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="842" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>5</v>
       </c>
@@ -36998,7 +36999,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="843" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>5</v>
       </c>
@@ -37039,7 +37040,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="844" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>5</v>
       </c>
@@ -37080,7 +37081,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="845" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>5</v>
       </c>
@@ -37121,7 +37122,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="846" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>5</v>
       </c>
@@ -37162,7 +37163,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="847" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>5</v>
       </c>
@@ -37203,7 +37204,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="848" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>5</v>
       </c>
@@ -37244,7 +37245,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="849" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>5</v>
       </c>
@@ -37285,7 +37286,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="850" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>5</v>
       </c>
@@ -37326,7 +37327,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="851" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>5</v>
       </c>
@@ -37367,7 +37368,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="852" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>5</v>
       </c>
@@ -37408,7 +37409,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="853" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>5</v>
       </c>
@@ -37449,7 +37450,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="854" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>5</v>
       </c>
@@ -37490,7 +37491,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="855" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>5</v>
       </c>
@@ -37531,7 +37532,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="856" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>5</v>
       </c>
@@ -37572,7 +37573,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="857" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>5</v>
       </c>
@@ -37613,7 +37614,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="858" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>5</v>
       </c>
@@ -37654,7 +37655,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="859" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>5</v>
       </c>
@@ -37695,7 +37696,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="860" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>5</v>
       </c>
@@ -37736,7 +37737,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="861" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>5</v>
       </c>
@@ -37777,7 +37778,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="862" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>5</v>
       </c>
@@ -37818,7 +37819,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="863" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>5</v>
       </c>
@@ -37859,7 +37860,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="864" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>5</v>
       </c>
@@ -37900,7 +37901,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="865" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>5</v>
       </c>
@@ -37941,7 +37942,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="866" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>5</v>
       </c>
@@ -37982,7 +37983,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="867" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>5</v>
       </c>
@@ -38023,7 +38024,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="868" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>5</v>
       </c>
@@ -38064,7 +38065,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="869" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>5</v>
       </c>
@@ -38105,7 +38106,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="870" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>5</v>
       </c>
@@ -38146,7 +38147,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="871" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>5</v>
       </c>
@@ -38187,7 +38188,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="872" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>5</v>
       </c>
@@ -38228,7 +38229,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="873" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>5</v>
       </c>
@@ -38269,7 +38270,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="874" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>5</v>
       </c>
@@ -38310,7 +38311,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="875" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>5</v>
       </c>
@@ -38351,7 +38352,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="876" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>5</v>
       </c>
@@ -38392,7 +38393,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="877" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>5</v>
       </c>
@@ -38433,7 +38434,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="878" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>5</v>
       </c>
@@ -38474,7 +38475,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="879" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>5</v>
       </c>
@@ -38515,7 +38516,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="880" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>5</v>
       </c>
@@ -38556,7 +38557,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="881" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>5</v>
       </c>
@@ -38597,7 +38598,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="882" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>5</v>
       </c>
@@ -38638,7 +38639,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="883" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>5</v>
       </c>
@@ -38679,7 +38680,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="884" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>5</v>
       </c>
@@ -38720,7 +38721,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="885" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>5</v>
       </c>
@@ -38761,7 +38762,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="886" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>5</v>
       </c>
@@ -38802,7 +38803,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="887" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>5</v>
       </c>
@@ -38843,7 +38844,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="888" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>5</v>
       </c>
@@ -38884,7 +38885,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="889" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>5</v>
       </c>
@@ -38925,7 +38926,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="890" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>5</v>
       </c>
@@ -38966,7 +38967,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="891" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>5</v>
       </c>
@@ -39007,7 +39008,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="892" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>5</v>
       </c>
@@ -39048,7 +39049,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="893" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>5</v>
       </c>
@@ -39089,7 +39090,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="894" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>5</v>
       </c>
@@ -39130,7 +39131,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="895" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>5</v>
       </c>
@@ -39171,7 +39172,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="896" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>5</v>
       </c>
@@ -39212,7 +39213,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="897" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>5</v>
       </c>
@@ -39253,7 +39254,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="898" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>5</v>
       </c>
@@ -39294,7 +39295,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="899" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>5</v>
       </c>
@@ -39335,7 +39336,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="900" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>5</v>
       </c>
@@ -39376,7 +39377,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="901" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>5</v>
       </c>
@@ -39417,7 +39418,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="902" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>5</v>
       </c>
@@ -39458,7 +39459,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="903" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>5</v>
       </c>
@@ -39499,7 +39500,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="904" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>5</v>
       </c>
@@ -39540,7 +39541,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="905" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>5</v>
       </c>
@@ -39581,7 +39582,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="906" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>5</v>
       </c>
@@ -39622,7 +39623,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="907" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>5</v>
       </c>
@@ -39663,7 +39664,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="908" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>5</v>
       </c>
@@ -39704,7 +39705,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="909" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>5</v>
       </c>
@@ -39745,7 +39746,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="910" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>5</v>
       </c>
@@ -39786,7 +39787,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="911" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>5</v>
       </c>
@@ -39827,7 +39828,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="912" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>5</v>
       </c>
@@ -39868,7 +39869,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="913" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>5</v>
       </c>
@@ -39909,7 +39910,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="914" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>5</v>
       </c>
@@ -39950,7 +39951,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="915" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>5</v>
       </c>
@@ -39991,7 +39992,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="916" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>5</v>
       </c>
@@ -40032,7 +40033,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="917" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>5</v>
       </c>
@@ -40073,7 +40074,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="918" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>5</v>
       </c>
@@ -40115,6 +40116,23 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M918" xr:uid="{2D6820A2-C4B6-4EF0-94DD-4395E6273D53}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Twist"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="PANTOLON"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Kumaş Tipi"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
